--- a/UzTMK/UzTMK_BankBP_Sarikul.xlsx
+++ b/UzTMK/UzTMK_BankBP_Sarikul.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Резюме" sheetId="1" state="hidden" r:id="rId3"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="520">
   <si>
     <t xml:space="preserve">БИЗНЕС-ПЛАН ИНВЕСТИЦИОННОГО ПРОЕКТА</t>
   </si>
@@ -286,7 +286,7 @@
     <t xml:space="preserve">- Все затраты сверх суммы кредита финансируются за счёт собственных средств заемщика.</t>
   </si>
   <si>
-    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года капитализируются в стоимость основных средств.</t>
+    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года отражаются в расходах 1-го года и оплачиваются за счёт собственных средств заемщика.</t>
   </si>
   <si>
     <t xml:space="preserve">- Резерв на непредвиденные расходы - 1% суммы кредита.</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">Приложение 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Линейный метод. Проценты льготного периода капитализированы в стоимость основных средств (МСФО IAS 23).</t>
+    <t xml:space="preserve">Линейный метод.</t>
   </si>
   <si>
     <t xml:space="preserve">ОБЪЕКТЫ АМОРТИЗАЦИИ</t>
@@ -680,12 +680,6 @@
     <t xml:space="preserve">Поддерживающие капвложения (% от первоначальной стоимости ОС)</t>
   </si>
   <si>
-    <t xml:space="preserve">Капитализированные проценты по кредиту за льготный период (1-й год)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Затраты по займам (МСФО IAS 23)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Х</t>
   </si>
   <si>
@@ -1244,7 +1238,7 @@
     <t xml:space="preserve">ФИНАНСОВЫЕ ИЗДЕРЖКИ</t>
   </si>
   <si>
-    <t xml:space="preserve">   Проценты за кредит (1-й год - капитализированы, оплачены за счёт собственных средств)</t>
+    <t xml:space="preserve">   Проценты за кредит (1-й год - за счёт собственных средств заемщика)</t>
   </si>
   <si>
     <t xml:space="preserve">ПОЛНАЯ СТОИМОСТЬ ПРОДАННОЙ ПРОДУКЦИИ</t>
@@ -1397,7 +1391,7 @@
     <t xml:space="preserve">Долг / EBITDA</t>
   </si>
   <si>
-    <t xml:space="preserve">1-й год: проценты за кредит льготного периода оплачиваются за счёт собственных средств и капитализируются в стоимость основных средств (МСФО IAS 23, Приложения 1 и 4); в отчёт о прибылях и убытках не включаются.</t>
+    <t xml:space="preserve">1-й год: проценты за кредит льготного периода отражены в расходах 1-го года и оплачиваются за счёт собственных средств заемщика (включены в стоимость проекта, Приложение 1).</t>
   </si>
   <si>
     <t xml:space="preserve">ПРЕДПОЛОЖЕНИЯ ПО РАБОЧЕМУ КАПИТАЛУ (в экв. долл. США)</t>
@@ -1517,7 +1511,7 @@
     <t xml:space="preserve">Проценты за кредит (B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период (проценты льготного периода)</t>
+    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период</t>
   </si>
   <si>
     <t xml:space="preserve">Чистые поступления наличности</t>
@@ -2126,14 +2120,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2143,6 +2129,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2204,6 +2194,10 @@
     </xf>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3000,7 +2994,7 @@
       </c>
       <c r="F39" s="13" t="n">
         <f aca="false">ProfLoss!F27</f>
-        <v>56029868.7189859</v>
+        <v>56029868.7189858</v>
       </c>
       <c r="G39" s="13" t="n">
         <f aca="false">ProfLoss!G27</f>
@@ -3012,7 +3006,7 @@
       </c>
       <c r="I39" s="13" t="n">
         <f aca="false">ProfLoss!I27</f>
-        <v>53069156.5496527</v>
+        <v>53069156.5496526</v>
       </c>
       <c r="J39" s="13" t="n">
         <f aca="false">ProfLoss!J27</f>
@@ -3028,31 +3022,31 @@
       </c>
       <c r="D40" s="13" t="n">
         <f aca="false">ProfLoss!D22</f>
-        <v>3541570.50918427</v>
+        <v>779649.643650383</v>
       </c>
       <c r="E40" s="13" t="n">
         <f aca="false">ProfLoss!E22</f>
-        <v>19438642.589987</v>
+        <v>19567692.4884224</v>
       </c>
       <c r="F40" s="13" t="n">
         <f aca="false">ProfLoss!F22</f>
-        <v>21292481.692468</v>
+        <v>21421531.5909034</v>
       </c>
       <c r="G40" s="13" t="n">
         <f aca="false">ProfLoss!G22</f>
-        <v>24368803.2111427</v>
+        <v>24497853.1095781</v>
       </c>
       <c r="H40" s="13" t="n">
         <f aca="false">ProfLoss!H22</f>
-        <v>15587710.1876556</v>
+        <v>15716760.086091</v>
       </c>
       <c r="I40" s="13" t="n">
         <f aca="false">ProfLoss!I22</f>
-        <v>16481055.7349056</v>
+        <v>16610105.6333409</v>
       </c>
       <c r="J40" s="13" t="n">
         <f aca="false">ProfLoss!J22</f>
-        <v>17415037.3715825</v>
+        <v>17544087.2700179</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3064,31 +3058,31 @@
       </c>
       <c r="D41" s="13" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-16752460.6342135</v>
+        <v>-16528521.1045756</v>
       </c>
       <c r="E41" s="13" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>52390242.0836931</v>
+        <v>52367468.5722045</v>
       </c>
       <c r="F41" s="13" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>42237651.1643225</v>
+        <v>42214877.6528339</v>
       </c>
       <c r="G41" s="13" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>40056297.6941421</v>
+        <v>40033524.1826535</v>
       </c>
       <c r="H41" s="13" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>33451740.2727095</v>
+        <v>33428966.7612209</v>
       </c>
       <c r="I41" s="13" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>33632223.371841</v>
+        <v>33609449.8603524</v>
       </c>
       <c r="J41" s="13" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>34187694.5143001</v>
+        <v>34164921.0028116</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3136,31 +3130,31 @@
       </c>
       <c r="D43" s="13" t="n">
         <f aca="false">CashFlow!D26</f>
-        <v>10043302.5024297</v>
+        <v>10267242.0320676</v>
       </c>
       <c r="E43" s="13" t="n">
         <f aca="false">CashFlow!E26</f>
-        <v>41036542.4656462</v>
+        <v>41013768.9541576</v>
       </c>
       <c r="F43" s="13" t="n">
         <f aca="false">CashFlow!F26</f>
-        <v>31398233.1273804</v>
+        <v>31375459.6158918</v>
       </c>
       <c r="G43" s="13" t="n">
         <f aca="false">CashFlow!G26</f>
-        <v>29722957.6902799</v>
+        <v>29700184.1787913</v>
       </c>
       <c r="H43" s="13" t="n">
         <f aca="false">CashFlow!H26</f>
-        <v>23624478.3019273</v>
+        <v>23601704.7904388</v>
       </c>
       <c r="I43" s="13" t="n">
         <f aca="false">CashFlow!I26</f>
-        <v>24308381.9467505</v>
+        <v>24285608.4352619</v>
       </c>
       <c r="J43" s="13" t="n">
         <f aca="false">CashFlow!J26</f>
-        <v>25372588.6096779</v>
+        <v>25349815.0981893</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3172,31 +3166,31 @@
       </c>
       <c r="D44" s="13" t="n">
         <f aca="false">CashFlow!D27</f>
-        <v>10043302.5024297</v>
+        <v>10267242.0320676</v>
       </c>
       <c r="E44" s="13" t="n">
         <f aca="false">CashFlow!E27</f>
-        <v>51079844.9680759</v>
+        <v>51281010.9862252</v>
       </c>
       <c r="F44" s="13" t="n">
         <f aca="false">CashFlow!F27</f>
-        <v>82478078.0954563</v>
+        <v>82656470.6021169</v>
       </c>
       <c r="G44" s="13" t="n">
         <f aca="false">CashFlow!G27</f>
-        <v>112201035.785736</v>
+        <v>112356654.780908</v>
       </c>
       <c r="H44" s="13" t="n">
         <f aca="false">CashFlow!H27</f>
-        <v>135825514.087664</v>
+        <v>135958359.571347</v>
       </c>
       <c r="I44" s="13" t="n">
         <f aca="false">CashFlow!I27</f>
-        <v>160133896.034414</v>
+        <v>160243968.006609</v>
       </c>
       <c r="J44" s="13" t="n">
         <f aca="false">CashFlow!J27</f>
-        <v>185506484.644092</v>
+        <v>185593783.104798</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3212,27 +3206,27 @@
       </c>
       <c r="E45" s="20" t="n">
         <f aca="false">CashFlow!E30</f>
-        <v>5.12748176681465</v>
+        <v>5.12519119241954</v>
       </c>
       <c r="F45" s="20" t="n">
         <f aca="false">CashFlow!F30</f>
-        <v>4.3303211933182</v>
+        <v>4.3279056717935</v>
       </c>
       <c r="G45" s="20" t="n">
         <f aca="false">CashFlow!G30</f>
-        <v>4.33145625972355</v>
+        <v>4.32890372244933</v>
       </c>
       <c r="H45" s="20" t="n">
         <f aca="false">CashFlow!H30</f>
-        <v>3.8071466224298</v>
+        <v>3.80444059078588</v>
       </c>
       <c r="I45" s="20" t="n">
         <f aca="false">CashFlow!I30</f>
-        <v>4.07218321343031</v>
+        <v>4.069305012822</v>
       </c>
       <c r="J45" s="20" t="n">
         <f aca="false">CashFlow!J30</f>
-        <v>4.42702517516834</v>
+        <v>4.42394920218037</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3291,7 +3285,7 @@
       </c>
       <c r="C49" s="21" t="n">
         <f aca="false">NPV_IRR!D18</f>
-        <v>4579191.18347016</v>
+        <v>4694677.7199059</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3300,7 +3294,7 @@
       </c>
       <c r="C50" s="22" t="n">
         <f aca="false">NPV_IRR!D19</f>
-        <v>0.125981395703447</v>
+        <v>0.12630736634052</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3309,7 +3303,7 @@
       </c>
       <c r="C51" s="23" t="n">
         <f aca="false">NPV_IRR!D20</f>
-        <v>1.03220363852201</v>
+        <v>1.03306256222008</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3318,7 +3312,7 @@
       </c>
       <c r="C52" s="24" t="n">
         <f aca="false">NPV_IRR!D21</f>
-        <v>4.87127394389732</v>
+        <v>4.86703323597043</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3327,7 +3321,7 @@
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">NPV_IRR!D22</f>
-        <v>6.7030576446765</v>
+        <v>6.69535713052309</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3336,7 +3330,7 @@
       </c>
       <c r="C54" s="25" t="str">
         <f aca="false">TEXT(CashFlow!D31,"0.00") &amp; "x / " &amp; TEXT(CashFlow!D32,"0.00") &amp; "x"</f>
-        <v>3.81x / 4.35x</v>
+        <v>3.80x / 4.35x</v>
       </c>
       <c r="D54" s="25"/>
       <c r="E54" s="25"/>
@@ -3347,7 +3341,7 @@
       </c>
       <c r="C55" s="22" t="n">
         <f aca="false">BreakPoint!C10</f>
-        <v>0.393358554791275</v>
+        <v>0.390884162378221</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3561,7 +3555,7 @@
       </c>
       <c r="C75" s="6" t="str">
         <f aca="false">"Освоение мощности: 1-й год - " &amp; TEXT(ProdPlan!D11,"0%") &amp; ", 2-й год - " &amp; TEXT(ProdPlan!E11,"0%") &amp; ", 3-й год - " &amp; TEXT(ProdPlan!F11,"0%") &amp; "; льготный период 12 мес. и запас DSCR (мин. " &amp; TEXT(CashFlow!D31,"0.00") &amp; "x) покрывают период выхода на мощность."</f>
-        <v>Освоение мощности: 1-й год - 16%, 2-й год - 56%, 3-й год - 60%; льготный период 12 мес. и запас DSCR (мин. 3.81x) покрывают период выхода на мощность.</v>
+        <v>Освоение мощности: 1-й год - 16%, 2-й год - 56%, 3-й год - 60%; льготный период 12 мес. и запас DSCR (мин. 3.80x) покрывают период выхода на мощность.</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -3672,10 +3666,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3683,27 +3677,27 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E5" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>250</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3713,10 +3707,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
@@ -3726,10 +3720,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -3739,27 +3733,27 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
+        <v>277</v>
+      </c>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
       <c r="F9" s="61" t="n">
         <f aca="false">SUM(F6:F8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="86" t="s">
-        <v>280</v>
+      <c r="B10" s="85" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F11" s="87" t="s">
-        <v>282</v>
+        <v>279</v>
+      </c>
+      <c r="F11" s="86" t="s">
+        <v>280</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>0.12</v>
@@ -3770,40 +3764,40 @@
         <v>44</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="F12" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="G12" s="18" t="s">
         <v>285</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
+        <v>286</v>
+      </c>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C14" s="80" t="n">
+        <v>287</v>
+      </c>
+      <c r="C14" s="79" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">IFERROR(F14/C14/12,0)</f>
@@ -3819,13 +3813,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" s="80" t="n">
+        <v>289</v>
+      </c>
+      <c r="C15" s="79" t="n">
         <v>31</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E15" s="13" t="n">
         <f aca="false">IFERROR(F15/C15/12,0)</f>
@@ -3841,13 +3835,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C16" s="80" t="n">
+        <v>290</v>
+      </c>
+      <c r="C16" s="79" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">IFERROR(F16/C16/12,0)</f>
@@ -3863,13 +3857,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="C17" s="80" t="n">
+        <v>291</v>
+      </c>
+      <c r="C17" s="79" t="n">
         <v>32</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E17" s="13" t="n">
         <f aca="false">IFERROR(F17/C17/12,0)</f>
@@ -3885,13 +3879,13 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" s="80" t="n">
+        <v>292</v>
+      </c>
+      <c r="C18" s="79" t="n">
         <v>9</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">IFERROR(F18/C18/12,0)</f>
@@ -3907,13 +3901,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C19" s="80" t="n">
+        <v>293</v>
+      </c>
+      <c r="C19" s="79" t="n">
         <v>47</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E19" s="13" t="n">
         <f aca="false">IFERROR(F19/C19/12,0)</f>
@@ -3929,13 +3923,13 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C20" s="80" t="n">
+        <v>294</v>
+      </c>
+      <c r="C20" s="79" t="n">
         <v>9</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E20" s="13" t="n">
         <f aca="false">IFERROR(F20/C20/12,0)</f>
@@ -3951,13 +3945,13 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="C21" s="80" t="n">
+        <v>295</v>
+      </c>
+      <c r="C21" s="79" t="n">
         <v>33</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E21" s="13" t="n">
         <f aca="false">IFERROR(F21/C21/12,0)</f>
@@ -3973,13 +3967,13 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C22" s="80" t="n">
+        <v>296</v>
+      </c>
+      <c r="C22" s="79" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">IFERROR(F22/C22/12,0)</f>
@@ -3995,13 +3989,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="80" t="n">
+        <v>297</v>
+      </c>
+      <c r="C23" s="79" t="n">
         <v>19</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E23" s="13" t="n">
         <f aca="false">IFERROR(F23/C23/12,0)</f>
@@ -4017,13 +4011,13 @@
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C24" s="80" t="n">
+        <v>298</v>
+      </c>
+      <c r="C24" s="79" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E24" s="13" t="n">
         <f aca="false">IFERROR(F24/C24/12,0)</f>
@@ -4039,13 +4033,13 @@
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C25" s="80" t="n">
+        <v>299</v>
+      </c>
+      <c r="C25" s="79" t="n">
         <v>17</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">IFERROR(F25/C25/12,0)</f>
@@ -4061,13 +4055,13 @@
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C26" s="80" t="n">
+        <v>300</v>
+      </c>
+      <c r="C26" s="79" t="n">
         <v>56</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">IFERROR(F26/C26/12,0)</f>
@@ -4085,7 +4079,7 @@
       <c r="B27" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="C27" s="88" t="n">
+      <c r="C27" s="87" t="n">
         <f aca="false">SUM(C14:C26)</f>
         <v>277</v>
       </c>
@@ -4102,36 +4096,36 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
+        <v>301</v>
+      </c>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
       <c r="F28" s="61" t="n">
         <f aca="false">F27+G27</f>
         <v>7246535.39613101</v>
       </c>
-      <c r="G28" s="82"/>
+      <c r="G28" s="81"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
+        <v>302</v>
+      </c>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C31" s="80" t="n">
+        <v>303</v>
+      </c>
+      <c r="C31" s="79" t="n">
         <v>7</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E31" s="13" t="n">
         <f aca="false">IFERROR(F31/C31/12,0)</f>
@@ -4147,13 +4141,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C32" s="80" t="n">
+        <v>304</v>
+      </c>
+      <c r="C32" s="79" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E32" s="13" t="n">
         <f aca="false">IFERROR(F32/C32/12,0)</f>
@@ -4169,13 +4163,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="C33" s="80" t="n">
+        <v>305</v>
+      </c>
+      <c r="C33" s="79" t="n">
         <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E33" s="13" t="n">
         <f aca="false">IFERROR(F33/C33/12,0)</f>
@@ -4191,13 +4185,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C34" s="80" t="n">
+        <v>306</v>
+      </c>
+      <c r="C34" s="79" t="n">
         <v>6</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E34" s="13" t="n">
         <f aca="false">IFERROR(F34/C34/12,0)</f>
@@ -4213,13 +4207,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C35" s="80" t="n">
+        <v>307</v>
+      </c>
+      <c r="C35" s="79" t="n">
         <v>15</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E35" s="13" t="n">
         <f aca="false">IFERROR(F35/C35/12,0)</f>
@@ -4235,13 +4229,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="C36" s="80" t="n">
+        <v>308</v>
+      </c>
+      <c r="C36" s="79" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E36" s="13" t="n">
         <f aca="false">IFERROR(F36/C36/12,0)</f>
@@ -4257,13 +4251,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C37" s="80" t="n">
+        <v>309</v>
+      </c>
+      <c r="C37" s="79" t="n">
         <v>4</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E37" s="13" t="n">
         <f aca="false">IFERROR(F37/C37/12,0)</f>
@@ -4279,13 +4273,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="C38" s="80" t="n">
+        <v>310</v>
+      </c>
+      <c r="C38" s="79" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E38" s="13" t="n">
         <f aca="false">IFERROR(F38/C38/12,0)</f>
@@ -4301,13 +4295,13 @@
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C39" s="80" t="n">
+        <v>311</v>
+      </c>
+      <c r="C39" s="79" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E39" s="13" t="n">
         <f aca="false">IFERROR(F39/C39/12,0)</f>
@@ -4325,7 +4319,7 @@
       <c r="B40" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="C40" s="88" t="n">
+      <c r="C40" s="87" t="n">
         <f aca="false">SUM(C31:C39)</f>
         <v>59</v>
       </c>
@@ -4342,36 +4336,36 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
+        <v>301</v>
+      </c>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
       <c r="F41" s="61" t="n">
         <f aca="false">F40+G40</f>
         <v>1870445.3523864</v>
       </c>
-      <c r="G41" s="82"/>
+      <c r="G41" s="81"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="C43" s="89" t="n">
+        <v>312</v>
+      </c>
+      <c r="C43" s="88" t="n">
         <f aca="false">C27+C40</f>
         <v>336</v>
       </c>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
       <c r="F43" s="16" t="n">
         <f aca="false">F28+F41</f>
         <v>9116980.74851741</v>
       </c>
-      <c r="G43" s="85"/>
+      <c r="G43" s="84"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4401,10 +4395,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4412,7 +4406,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>46</v>
@@ -4449,9 +4443,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="82"/>
+        <v>317</v>
+      </c>
+      <c r="C6" s="81"/>
       <c r="D6" s="61" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>2530637.31905316</v>
@@ -4483,10 +4477,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">CostSold!D32</f>
@@ -4519,7 +4513,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="13" t="n">
@@ -4553,10 +4547,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">CostSold!D34</f>
@@ -4589,7 +4583,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="13" t="n">
@@ -4623,10 +4617,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>761994.89625</v>
@@ -4652,78 +4646,78 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="82"/>
+        <v>326</v>
+      </c>
+      <c r="C13" s="81"/>
       <c r="D13" s="61" t="n">
         <f aca="false">D14+D15</f>
-        <v>2205838.25258854</v>
+        <v>1981898.72295066</v>
       </c>
       <c r="E13" s="61" t="n">
         <f aca="false">E14+E15</f>
-        <v>23056840.3404719</v>
+        <v>23079613.8519605</v>
       </c>
       <c r="F13" s="61" t="n">
         <f aca="false">F14+F15</f>
-        <v>25123649.6122134</v>
+        <v>25146423.123702</v>
       </c>
       <c r="G13" s="61" t="n">
         <f aca="false">G14+G15</f>
-        <v>31964119.0247687</v>
+        <v>31986892.5362573</v>
       </c>
       <c r="H13" s="61" t="n">
         <f aca="false">H14+H15</f>
-        <v>29808987.164862</v>
+        <v>29831760.6763506</v>
       </c>
       <c r="I13" s="61" t="n">
         <f aca="false">I14+I15</f>
-        <v>30545023.1203278</v>
+        <v>30567796.6318164</v>
       </c>
       <c r="J13" s="61" t="n">
         <f aca="false">J14+J15</f>
-        <v>31321697.8979781</v>
+        <v>31344471.4094667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="13" t="n">
         <f aca="false">ProfLoss!D21</f>
-        <v>2205838.25258854</v>
+        <v>1981898.72295066</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">ProfLoss!E21</f>
-        <v>14757263.3710805</v>
+        <v>14780036.8825691</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">ProfLoss!F21</f>
-        <v>16276350.5249837</v>
+        <v>16299124.0364723</v>
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">ProfLoss!G21</f>
-        <v>20554660.7683254</v>
+        <v>20577434.279814</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">ProfLoss!H21</f>
-        <v>18721079.1836114</v>
+        <v>18743852.6951</v>
       </c>
       <c r="I14" s="13" t="n">
         <f aca="false">ProfLoss!I21</f>
-        <v>19219212.3536359</v>
+        <v>19241985.8651245</v>
       </c>
       <c r="J14" s="13" t="n">
         <f aca="false">ProfLoss!J21</f>
-        <v>19742934.7725243</v>
+        <v>19765708.2840129</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D15" s="13" t="n">
         <f aca="false">MAX(0,D22)</f>
@@ -4756,46 +4750,46 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="38" t="s">
-        <v>331</v>
-      </c>
-      <c r="C16" s="83"/>
+        <v>329</v>
+      </c>
+      <c r="C16" s="82"/>
       <c r="D16" s="16" t="n">
         <f aca="false">D6+D13</f>
-        <v>4736475.5716417</v>
+        <v>4512536.04200382</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">E6+E13</f>
-        <v>27703091.6305899</v>
+        <v>27725865.1420785</v>
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">F6+F13</f>
-        <v>30091150.8898287</v>
+        <v>30113924.4013173</v>
       </c>
       <c r="G16" s="16" t="n">
         <f aca="false">G6+G13</f>
-        <v>49159688.0475964</v>
+        <v>49182461.559085</v>
       </c>
       <c r="H16" s="16" t="n">
         <f aca="false">H6+H13</f>
-        <v>54473658.350503</v>
+        <v>54496431.8619916</v>
       </c>
       <c r="I16" s="16" t="n">
         <f aca="false">I6+I13</f>
-        <v>55796291.6480804</v>
+        <v>55819065.1595689</v>
       </c>
       <c r="J16" s="16" t="n">
         <f aca="false">J6+J13</f>
-        <v>57206552.4782851</v>
+        <v>57229325.9897737</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="37" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="13" t="n">
@@ -4822,7 +4816,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="13" t="n">
@@ -4849,7 +4843,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="13" t="n">
@@ -4876,7 +4870,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="28" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="21" t="n">
@@ -4910,46 +4904,46 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="37" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="13" t="n">
         <f aca="false">ProfLoss!D20</f>
-        <v>5747408.76177281</v>
+        <v>2761548.36660104</v>
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">ProfLoss!E20</f>
-        <v>34195905.9610675</v>
+        <v>34347729.3709915</v>
       </c>
       <c r="F25" s="13" t="n">
         <f aca="false">ProfLoss!F20</f>
-        <v>37568832.2174517</v>
+        <v>37720655.6273757</v>
       </c>
       <c r="G25" s="13" t="n">
         <f aca="false">ProfLoss!G20</f>
-        <v>44923463.9794681</v>
+        <v>45075287.3893921</v>
       </c>
       <c r="H25" s="13" t="n">
         <f aca="false">ProfLoss!H20</f>
-        <v>34308789.371267</v>
+        <v>34460612.781191</v>
       </c>
       <c r="I25" s="13" t="n">
         <f aca="false">ProfLoss!I20</f>
-        <v>35700268.0885415</v>
+        <v>35852091.4984654</v>
       </c>
       <c r="J25" s="13" t="n">
         <f aca="false">ProfLoss!J20</f>
-        <v>37157972.1441068</v>
+        <v>37309795.5540308</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="13" t="n">
@@ -4976,44 +4970,44 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="13" t="n">
         <f aca="false">D25+D26</f>
-        <v>29411176.7011805</v>
+        <v>26425316.3060087</v>
       </c>
       <c r="E27" s="13" t="n">
         <f aca="false">E25+E26</f>
-        <v>98381755.8072036</v>
+        <v>98533579.2171276</v>
       </c>
       <c r="F27" s="13" t="n">
         <f aca="false">F25+F26</f>
-        <v>108509003.499891</v>
+        <v>108660826.909815</v>
       </c>
       <c r="G27" s="13" t="n">
         <f aca="false">G25+G26</f>
-        <v>137031071.788836</v>
+        <v>137182895.19876</v>
       </c>
       <c r="H27" s="13" t="n">
         <f aca="false">H25+H26</f>
-        <v>124807194.557409</v>
+        <v>124959017.967333</v>
       </c>
       <c r="I27" s="13" t="n">
         <f aca="false">I25+I26</f>
-        <v>128128082.357573</v>
+        <v>128279905.767497</v>
       </c>
       <c r="J27" s="13" t="n">
         <f aca="false">J25+J26</f>
-        <v>131619565.150162</v>
+        <v>131771388.560086</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>0.075</v>
@@ -5039,36 +5033,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="21" t="n">
-        <f aca="false">D27*D28</f>
-        <v>2205838.25258854</v>
+        <f aca="false">MAX(0,MIN(D27,SUM($D27:D27)))*D28</f>
+        <v>1981898.72295066</v>
       </c>
       <c r="E29" s="21" t="n">
-        <f aca="false">E27*E28</f>
-        <v>14757263.3710805</v>
+        <f aca="false">MAX(0,MIN(E27,SUM($D27:E27)))*E28</f>
+        <v>14780036.8825691</v>
       </c>
       <c r="F29" s="21" t="n">
-        <f aca="false">F27*F28</f>
-        <v>16276350.5249837</v>
+        <f aca="false">MAX(0,MIN(F27,SUM($D27:F27)))*F28</f>
+        <v>16299124.0364723</v>
       </c>
       <c r="G29" s="21" t="n">
-        <f aca="false">G27*G28</f>
-        <v>20554660.7683254</v>
+        <f aca="false">MAX(0,MIN(G27,SUM($D27:G27)))*G28</f>
+        <v>20577434.279814</v>
       </c>
       <c r="H29" s="21" t="n">
-        <f aca="false">H27*H28</f>
-        <v>18721079.1836114</v>
+        <f aca="false">MAX(0,MIN(H27,SUM($D27:H27)))*H28</f>
+        <v>18743852.6951</v>
       </c>
       <c r="I29" s="21" t="n">
-        <f aca="false">I27*I28</f>
-        <v>19219212.3536359</v>
+        <f aca="false">MAX(0,MIN(I27,SUM($D27:I27)))*I28</f>
+        <v>19241985.8651245</v>
       </c>
       <c r="J29" s="21" t="n">
-        <f aca="false">J27*J28</f>
-        <v>19742934.7725243</v>
+        <f aca="false">MAX(0,MIN(J27,SUM($D27:J27)))*J28</f>
+        <v>19765708.2840129</v>
       </c>
     </row>
   </sheetData>
@@ -5111,40 +5105,40 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H2" s="59" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="60" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="F5" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="G5" s="18" t="s">
         <v>349</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="25" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C6" s="21" t="n">
         <f aca="false">C7+C8</f>
@@ -5169,7 +5163,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">F7+G7</f>
@@ -5193,7 +5187,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">F8+G8</f>
@@ -5217,7 +5211,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">F9+G9</f>
@@ -5241,7 +5235,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">F10+G10</f>
@@ -5265,7 +5259,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">F11+G11</f>
@@ -5289,11 +5283,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">F12+G12</f>
-        <v>1531183.72960385</v>
+        <v>1500819.04761905</v>
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">IFERROR(F12/C12,0)</f>
@@ -5305,7 +5299,7 @@
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">RawMat!F20</f>
-        <v>1531183.72960385</v>
+        <v>1500819.04761905</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0</v>
@@ -5313,7 +5307,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">F13+G13</f>
@@ -5337,7 +5331,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">F14+G14</f>
@@ -5361,7 +5355,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">F15+G15</f>
@@ -5384,7 +5378,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">F16+G16</f>
@@ -5408,7 +5402,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">F17+G17</f>
@@ -5432,7 +5426,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">F18+G18</f>
@@ -5456,7 +5450,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">F19+G19</f>
@@ -5480,7 +5474,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">F20+G20</f>
@@ -5504,11 +5498,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">F21+G21</f>
-        <v>16304839.2829399</v>
+        <v>16153015.8730159</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">IFERROR(F21/C21,0)</f>
@@ -5519,8 +5513,8 @@
         <v>0</v>
       </c>
       <c r="F21" s="13" t="n">
-        <f aca="false">Depreciate!J19</f>
-        <v>16304839.2829399</v>
+        <f aca="false">Depreciate!J18</f>
+        <v>16153015.8730159</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>0</v>
@@ -5532,19 +5526,19 @@
       </c>
       <c r="C22" s="16" t="n">
         <f aca="false">SUM(C6:C21)-C6</f>
-        <v>77429470.1688078</v>
+        <v>77247282.076899</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">IFERROR(F22/C22,0)</f>
-        <v>0.374053501249975</v>
+        <v>0.372577203376728</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">IFERROR(G22/C22,0)</f>
-        <v>0.625946498750025</v>
+        <v>0.627422796623273</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">SUM(F6:F21)-F6</f>
-        <v>28962764.416573</v>
+        <v>28780576.3246643</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">SUM(G6:G21)-G6</f>
@@ -5553,16 +5547,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C22-C24</f>
-        <v>33924589.0866426</v>
+        <v>33742400.9947338</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>43504881.0821652</v>
@@ -5570,7 +5564,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">SalePlan!G14</f>
@@ -5579,20 +5573,20 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C27" s="90" t="n">
+        <v>368</v>
+      </c>
+      <c r="C27" s="89" t="n">
         <f aca="false">IFERROR(C22/C26,0)</f>
-        <v>0.634168088338975</v>
+        <v>0.63267591909499</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C28" s="13" t="n">
         <f aca="false">IFERROR(C22/ProdPlan!G13,0)</f>
-        <v>24171.9508551283</v>
+        <v>24115.0753322246</v>
       </c>
     </row>
   </sheetData>
@@ -5622,10 +5616,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5670,10 +5664,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D6" s="14" t="n">
         <f aca="false">ProdPlan!D11</f>
@@ -5706,12 +5700,12 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="37" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -5740,7 +5734,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>34</v>
@@ -5769,7 +5763,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>34</v>
@@ -5798,7 +5792,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>34</v>
@@ -5827,43 +5821,43 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="13" t="n">
-        <f aca="false">Depreciate!$G$20</f>
-        <v>5287922.61812281</v>
+        <f aca="false">Depreciate!$G$19</f>
+        <v>5237314.81481482</v>
       </c>
       <c r="E13" s="13" t="n">
-        <f aca="false">Depreciate!$H$20</f>
-        <v>16022553.5686541</v>
+        <f aca="false">Depreciate!$H$19</f>
+        <v>15870730.1587302</v>
       </c>
       <c r="F13" s="13" t="n">
-        <f aca="false">Depreciate!$I$20</f>
-        <v>16163696.425797</v>
+        <f aca="false">Depreciate!$I$19</f>
+        <v>16011873.015873</v>
       </c>
       <c r="G13" s="13" t="n">
-        <f aca="false">Depreciate!$J$20</f>
-        <v>16304839.2829399</v>
+        <f aca="false">Depreciate!$J$19</f>
+        <v>16153015.8730159</v>
       </c>
       <c r="H13" s="13" t="n">
-        <f aca="false">Depreciate!$K$20</f>
-        <v>16445982.1400827</v>
+        <f aca="false">Depreciate!$K$19</f>
+        <v>16294158.7301587</v>
       </c>
       <c r="I13" s="13" t="n">
-        <f aca="false">Depreciate!$L$20</f>
-        <v>16587124.9972256</v>
+        <f aca="false">Depreciate!$L$19</f>
+        <v>16435301.5873016</v>
       </c>
       <c r="J13" s="13" t="n">
-        <f aca="false">Depreciate!$M$20</f>
-        <v>16728267.8543684</v>
+        <f aca="false">Depreciate!$M$19</f>
+        <v>16576444.4444444</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>34</v>
@@ -5892,7 +5886,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>34</v>
@@ -5921,7 +5915,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>34</v>
@@ -5949,44 +5943,44 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="91" t="s">
-        <v>384</v>
-      </c>
-      <c r="C17" s="78" t="s">
+      <c r="B17" s="90" t="s">
+        <v>382</v>
+      </c>
+      <c r="C17" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">SUM(D9:D16)</f>
-        <v>16276481.9318695</v>
+        <v>16225874.1285615</v>
       </c>
       <c r="E17" s="61" t="n">
         <f aca="false">SUM(E9:E16)</f>
-        <v>43393967.3704768</v>
+        <v>43242143.9605528</v>
       </c>
       <c r="F17" s="61" t="n">
         <f aca="false">SUM(F9:F16)</f>
-        <v>49415800.9268948</v>
+        <v>49263977.5169708</v>
       </c>
       <c r="G17" s="61" t="n">
         <f aca="false">SUM(G9:G16)</f>
-        <v>58855325.1075174</v>
+        <v>58703501.6975933</v>
       </c>
       <c r="H17" s="61" t="n">
         <f aca="false">SUM(H9:H16)</f>
-        <v>59781367.9686795</v>
+        <v>59629544.5587555</v>
       </c>
       <c r="I17" s="61" t="n">
         <f aca="false">SUM(I9:I16)</f>
-        <v>60873328.7902009</v>
+        <v>60721505.3802769</v>
       </c>
       <c r="J17" s="61" t="n">
         <f aca="false">SUM(J9:J16)</f>
-        <v>61988781.2596441</v>
+        <v>61836957.84972</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>34</v>
@@ -6014,47 +6008,47 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="91" t="s">
-        <v>386</v>
-      </c>
-      <c r="C19" s="78" t="s">
+      <c r="B19" s="90" t="s">
+        <v>384</v>
+      </c>
+      <c r="C19" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="61" t="n">
         <f aca="false">D17+D18</f>
-        <v>11316650.7201236</v>
+        <v>11266042.9168156</v>
       </c>
       <c r="E19" s="61" t="n">
         <f aca="false">E17+E18</f>
-        <v>43392941.6724242</v>
+        <v>43241118.2625002</v>
       </c>
       <c r="F19" s="61" t="n">
         <f aca="false">F17+F18</f>
-        <v>49091211.8766119</v>
+        <v>48939388.4666879</v>
       </c>
       <c r="G19" s="61" t="n">
         <f aca="false">G17+G18</f>
-        <v>58338443.9283732</v>
+        <v>58186620.5184492</v>
       </c>
       <c r="H19" s="61" t="n">
         <f aca="false">H17+H18</f>
-        <v>59738918.0634507</v>
+        <v>59587094.6535267</v>
       </c>
       <c r="I19" s="61" t="n">
         <f aca="false">I17+I18</f>
-        <v>60820556.2151245</v>
+        <v>60668732.8052005</v>
       </c>
       <c r="J19" s="61" t="n">
         <f aca="false">J17+J18</f>
-        <v>61934685.8487086</v>
+        <v>61782862.4387846</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -6080,43 +6074,43 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="13" t="n">
         <f aca="false">D19*D20</f>
-        <v>11316650.7201236</v>
+        <v>11266042.9168156</v>
       </c>
       <c r="E21" s="13" t="n">
         <f aca="false">E19*E20</f>
-        <v>43392941.6724242</v>
+        <v>43241118.2625002</v>
       </c>
       <c r="F21" s="13" t="n">
         <f aca="false">F19*F20</f>
-        <v>49091211.8766119</v>
+        <v>48939388.4666879</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">G19*G20</f>
-        <v>58338443.9283732</v>
+        <v>58186620.5184492</v>
       </c>
       <c r="H21" s="13" t="n">
         <f aca="false">H19*H20</f>
-        <v>59738918.0634507</v>
+        <v>59587094.6535267</v>
       </c>
       <c r="I21" s="13" t="n">
         <f aca="false">I19*I20</f>
-        <v>60820556.2151245</v>
+        <v>60668732.8052005</v>
       </c>
       <c r="J21" s="13" t="n">
         <f aca="false">J19*J20</f>
-        <v>61934685.8487086</v>
+        <v>61782862.4387846</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>34</v>
@@ -6152,12 +6146,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="37" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>34</v>
@@ -6186,43 +6180,43 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="13" t="n">
-        <f aca="false">Depreciate!$G$21</f>
+        <f aca="false">Depreciate!$G$20</f>
         <v>0</v>
       </c>
       <c r="E26" s="13" t="n">
-        <f aca="false">Depreciate!$H$21</f>
+        <f aca="false">Depreciate!$H$20</f>
         <v>0</v>
       </c>
       <c r="F26" s="13" t="n">
-        <f aca="false">Depreciate!$I$21</f>
+        <f aca="false">Depreciate!$I$20</f>
         <v>0</v>
       </c>
       <c r="G26" s="13" t="n">
-        <f aca="false">Depreciate!$J$21</f>
+        <f aca="false">Depreciate!$J$20</f>
         <v>0</v>
       </c>
       <c r="H26" s="13" t="n">
-        <f aca="false">Depreciate!$K$21</f>
+        <f aca="false">Depreciate!$K$20</f>
         <v>0</v>
       </c>
       <c r="I26" s="13" t="n">
-        <f aca="false">Depreciate!$L$21</f>
+        <f aca="false">Depreciate!$L$20</f>
         <v>0</v>
       </c>
       <c r="J26" s="13" t="n">
-        <f aca="false">Depreciate!$M$21</f>
+        <f aca="false">Depreciate!$M$20</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>34</v>
@@ -6251,7 +6245,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>34</v>
@@ -6279,10 +6273,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="91" t="s">
-        <v>395</v>
-      </c>
-      <c r="C29" s="78" t="s">
+      <c r="B29" s="90" t="s">
+        <v>393</v>
+      </c>
+      <c r="C29" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="61" t="n">
@@ -6316,12 +6310,12 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="37" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>34</v>
@@ -6350,7 +6344,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>34</v>
@@ -6379,7 +6373,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>34</v>
@@ -6408,7 +6402,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>34</v>
@@ -6437,7 +6431,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>34</v>
@@ -6465,10 +6459,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="91" t="s">
-        <v>399</v>
-      </c>
-      <c r="C37" s="78" t="s">
+      <c r="B37" s="90" t="s">
+        <v>397</v>
+      </c>
+      <c r="C37" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D37" s="61" t="n">
@@ -6502,18 +6496,19 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="37" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0</v>
+        <f aca="false">LOANS!$C$106</f>
+        <v>3036468.19847976</v>
       </c>
       <c r="E40" s="13" t="n">
         <f aca="false">LOANS!$D$106</f>
@@ -6542,74 +6537,74 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="38" t="s">
-        <v>402</v>
-      </c>
-      <c r="C42" s="83" t="s">
+        <v>400</v>
+      </c>
+      <c r="C42" s="82" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="16" t="n">
         <f aca="false">D19+D29+D37+D40</f>
-        <v>18114176.1705801</v>
+        <v>21100036.5657519</v>
       </c>
       <c r="E42" s="16" t="n">
         <f aca="false">E19+E29+E37+E40</f>
-        <v>50887662.4396244</v>
+        <v>50735839.0297004</v>
       </c>
       <c r="F42" s="16" t="n">
         <f aca="false">F19+F29+F37+F40</f>
-        <v>56468139.0174098</v>
+        <v>56316315.6074859</v>
       </c>
       <c r="G42" s="16" t="n">
         <f aca="false">G19+G29+G37+G40</f>
-        <v>77172667.302717</v>
+        <v>77020843.892793</v>
       </c>
       <c r="H42" s="16" t="n">
         <f aca="false">H19+H29+H37+H40</f>
-        <v>85654212.8522239</v>
+        <v>85502389.4422999</v>
       </c>
       <c r="I42" s="16" t="n">
         <f aca="false">I19+I29+I37+I40</f>
-        <v>86820322.9192439</v>
+        <v>86668499.50932</v>
       </c>
       <c r="J42" s="16" t="n">
         <f aca="false">J19+J29+J37+J40</f>
-        <v>88058558.119734</v>
+        <v>87906734.70981</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D43" s="13" t="n">
         <f aca="false">IFERROR(D42/(ProdPlan!D15+ProdPlan!D16),0)</f>
-        <v>27320.5274524371</v>
+        <v>31823.9219279708</v>
       </c>
       <c r="E43" s="13" t="n">
         <f aca="false">IFERROR(E42/(ProdPlan!E15+ProdPlan!E16),0)</f>
-        <v>21826.1116725108</v>
+        <v>21760.9934387261</v>
       </c>
       <c r="F43" s="13" t="n">
         <f aca="false">IFERROR(F42/(ProdPlan!F15+ProdPlan!F16),0)</f>
-        <v>22395.2262285705</v>
+        <v>22335.0131655724</v>
       </c>
       <c r="G43" s="13" t="n">
         <f aca="false">IFERROR(G42/(ProdPlan!G15+ProdPlan!G16),0)</f>
-        <v>24091.7820738482</v>
+        <v>24044.3858047617</v>
       </c>
       <c r="H43" s="13" t="n">
         <f aca="false">IFERROR(H42/(ProdPlan!H15+ProdPlan!H16),0)</f>
-        <v>27813.3603327924</v>
+        <v>27764.0607237416</v>
       </c>
       <c r="I43" s="13" t="n">
         <f aca="false">IFERROR(I42/(ProdPlan!I15+ProdPlan!I16),0)</f>
-        <v>28210.7998933697</v>
+        <v>28161.4674364923</v>
       </c>
       <c r="J43" s="13" t="n">
         <f aca="false">IFERROR(J42/(ProdPlan!J15+ProdPlan!J16),0)</f>
-        <v>28613.143541578</v>
+        <v>28563.8110847006</v>
       </c>
     </row>
   </sheetData>
@@ -6651,46 +6646,46 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H2" s="59" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="92" t="n">
+      <c r="C5" s="91" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$27</f>
         <v>84</v>
       </c>
-      <c r="D5" s="93" t="s">
-        <v>406</v>
+      <c r="D5" s="92" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="C6" s="92" t="n">
+        <v>405</v>
+      </c>
+      <c r="C6" s="91" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$28</f>
         <v>12</v>
       </c>
-      <c r="D6" s="93" t="s">
-        <v>406</v>
+      <c r="D6" s="92" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="C7" s="92" t="n">
+        <v>406</v>
+      </c>
+      <c r="C7" s="91" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$29</f>
         <v>12</v>
       </c>
-      <c r="D7" s="93" t="s">
-        <v>406</v>
+      <c r="D7" s="92" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6701,2862 +6696,2862 @@
         <f aca="false">ИНФОРМАЦИЯ!$C$26</f>
         <v>0.07</v>
       </c>
-      <c r="D8" s="93" t="s">
-        <v>409</v>
+      <c r="D8" s="92" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$25</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="92" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="C10" s="94" t="n">
+        <v>409</v>
+      </c>
+      <c r="C10" s="93" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$30</f>
         <v>46388</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="92"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="C11" s="92" t="n">
+        <v>410</v>
+      </c>
+      <c r="C11" s="91" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$31</f>
         <v>360</v>
       </c>
-      <c r="D11" s="93" t="s">
-        <v>413</v>
+      <c r="D11" s="92" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C12" s="92" t="n">
+        <v>412</v>
+      </c>
+      <c r="C12" s="91" t="n">
         <f aca="false">C5-C6</f>
         <v>72</v>
       </c>
-      <c r="D12" s="93" t="s">
-        <v>415</v>
+      <c r="D12" s="92" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="C13" s="81" t="n">
+        <v>414</v>
+      </c>
+      <c r="C13" s="80" t="n">
         <f aca="false">C9/C12</f>
         <v>594220.782481362</v>
       </c>
-      <c r="D13" s="93" t="s">
+      <c r="D13" s="92" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>417</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>419</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>125</v>
       </c>
       <c r="E15" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="G15" s="18" t="s">
         <v>420</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="H15" s="18" t="s">
         <v>421</v>
       </c>
-      <c r="G15" s="18" t="s">
-        <v>422</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>423</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="76" t="n">
+      <c r="A16" s="94" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="95" t="n">
         <f aca="false">EOMONTH($C$10,0)</f>
         <v>46418</v>
       </c>
-      <c r="C16" s="81" t="n">
+      <c r="C16" s="80" t="n">
         <f aca="false">$C$9</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D16" s="81" t="n">
+      <c r="D16" s="80" t="n">
         <f aca="false">IF(A16&gt;$C$6,MIN(C16,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="81" t="n">
+      <c r="E16" s="80" t="n">
         <f aca="false">C16*$C$8*DAY(B16)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F16" s="81" t="n">
+      <c r="F16" s="80" t="n">
         <f aca="false">D16+E16</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G16" s="81" t="n">
+      <c r="G16" s="80" t="n">
         <f aca="false">C16-D16</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H16" s="76" t="n">
+      <c r="H16" s="94" t="n">
         <f aca="false">YEAR(B16)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="76" t="n">
+      <c r="A17" s="94" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="95" t="n">
         <f aca="false">EOMONTH($C$10,1)</f>
         <v>46446</v>
       </c>
-      <c r="C17" s="81" t="n">
+      <c r="C17" s="80" t="n">
         <f aca="false">G16</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D17" s="81" t="n">
+      <c r="D17" s="80" t="n">
         <f aca="false">IF(A17&gt;$C$6,MIN(C17,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="81" t="n">
+      <c r="E17" s="80" t="n">
         <f aca="false">C17*$C$8*DAY(B17)/$C$11</f>
         <v>232934.546732694</v>
       </c>
-      <c r="F17" s="81" t="n">
+      <c r="F17" s="80" t="n">
         <f aca="false">D17+E17</f>
         <v>232934.546732694</v>
       </c>
-      <c r="G17" s="81" t="n">
+      <c r="G17" s="80" t="n">
         <f aca="false">C17-D17</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H17" s="76" t="n">
+      <c r="H17" s="94" t="n">
         <f aca="false">YEAR(B17)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="76" t="n">
+      <c r="A18" s="94" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="95" t="n">
         <f aca="false">EOMONTH($C$10,2)</f>
         <v>46477</v>
       </c>
-      <c r="C18" s="81" t="n">
+      <c r="C18" s="80" t="n">
         <f aca="false">G17</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D18" s="81" t="n">
+      <c r="D18" s="80" t="n">
         <f aca="false">IF(A18&gt;$C$6,MIN(C18,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="81" t="n">
+      <c r="E18" s="80" t="n">
         <f aca="false">C18*$C$8*DAY(B18)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F18" s="81" t="n">
+      <c r="F18" s="80" t="n">
         <f aca="false">D18+E18</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G18" s="81" t="n">
+      <c r="G18" s="80" t="n">
         <f aca="false">C18-D18</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H18" s="76" t="n">
+      <c r="H18" s="94" t="n">
         <f aca="false">YEAR(B18)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="76" t="n">
+      <c r="A19" s="94" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="95" t="n">
         <f aca="false">EOMONTH($C$10,3)</f>
         <v>46507</v>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="80" t="n">
         <f aca="false">G18</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D19" s="81" t="n">
+      <c r="D19" s="80" t="n">
         <f aca="false">IF(A19&gt;$C$6,MIN(C19,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="81" t="n">
+      <c r="E19" s="80" t="n">
         <f aca="false">C19*$C$8*DAY(B19)/$C$11</f>
         <v>249572.728642172</v>
       </c>
-      <c r="F19" s="81" t="n">
+      <c r="F19" s="80" t="n">
         <f aca="false">D19+E19</f>
         <v>249572.728642172</v>
       </c>
-      <c r="G19" s="81" t="n">
+      <c r="G19" s="80" t="n">
         <f aca="false">C19-D19</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H19" s="76" t="n">
+      <c r="H19" s="94" t="n">
         <f aca="false">YEAR(B19)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="76" t="n">
+      <c r="A20" s="94" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="95" t="n">
         <f aca="false">EOMONTH($C$10,4)</f>
         <v>46538</v>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="80" t="n">
         <f aca="false">G19</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D20" s="81" t="n">
+      <c r="D20" s="80" t="n">
         <f aca="false">IF(A20&gt;$C$6,MIN(C20,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="81" t="n">
+      <c r="E20" s="80" t="n">
         <f aca="false">C20*$C$8*DAY(B20)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F20" s="81" t="n">
+      <c r="F20" s="80" t="n">
         <f aca="false">D20+E20</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G20" s="81" t="n">
+      <c r="G20" s="80" t="n">
         <f aca="false">C20-D20</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H20" s="76" t="n">
+      <c r="H20" s="94" t="n">
         <f aca="false">YEAR(B20)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="76" t="n">
+      <c r="A21" s="94" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="95" t="n">
         <f aca="false">EOMONTH($C$10,5)</f>
         <v>46568</v>
       </c>
-      <c r="C21" s="81" t="n">
+      <c r="C21" s="80" t="n">
         <f aca="false">G20</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D21" s="81" t="n">
+      <c r="D21" s="80" t="n">
         <f aca="false">IF(A21&gt;$C$6,MIN(C21,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="81" t="n">
+      <c r="E21" s="80" t="n">
         <f aca="false">C21*$C$8*DAY(B21)/$C$11</f>
         <v>249572.728642172</v>
       </c>
-      <c r="F21" s="81" t="n">
+      <c r="F21" s="80" t="n">
         <f aca="false">D21+E21</f>
         <v>249572.728642172</v>
       </c>
-      <c r="G21" s="81" t="n">
+      <c r="G21" s="80" t="n">
         <f aca="false">C21-D21</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H21" s="76" t="n">
+      <c r="H21" s="94" t="n">
         <f aca="false">YEAR(B21)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="76" t="n">
+      <c r="A22" s="94" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="95" t="n">
         <f aca="false">EOMONTH($C$10,6)</f>
         <v>46599</v>
       </c>
-      <c r="C22" s="81" t="n">
+      <c r="C22" s="80" t="n">
         <f aca="false">G21</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D22" s="81" t="n">
+      <c r="D22" s="80" t="n">
         <f aca="false">IF(A22&gt;$C$6,MIN(C22,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="81" t="n">
+      <c r="E22" s="80" t="n">
         <f aca="false">C22*$C$8*DAY(B22)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F22" s="81" t="n">
+      <c r="F22" s="80" t="n">
         <f aca="false">D22+E22</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G22" s="81" t="n">
+      <c r="G22" s="80" t="n">
         <f aca="false">C22-D22</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H22" s="76" t="n">
+      <c r="H22" s="94" t="n">
         <f aca="false">YEAR(B22)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="76" t="n">
+      <c r="A23" s="94" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="95" t="n">
         <f aca="false">EOMONTH($C$10,7)</f>
         <v>46630</v>
       </c>
-      <c r="C23" s="81" t="n">
+      <c r="C23" s="80" t="n">
         <f aca="false">G22</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D23" s="81" t="n">
+      <c r="D23" s="80" t="n">
         <f aca="false">IF(A23&gt;$C$6,MIN(C23,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="81" t="n">
+      <c r="E23" s="80" t="n">
         <f aca="false">C23*$C$8*DAY(B23)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F23" s="81" t="n">
+      <c r="F23" s="80" t="n">
         <f aca="false">D23+E23</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G23" s="81" t="n">
+      <c r="G23" s="80" t="n">
         <f aca="false">C23-D23</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H23" s="76" t="n">
+      <c r="H23" s="94" t="n">
         <f aca="false">YEAR(B23)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="76" t="n">
+      <c r="A24" s="94" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="95" t="n">
         <f aca="false">EOMONTH($C$10,8)</f>
         <v>46660</v>
       </c>
-      <c r="C24" s="81" t="n">
+      <c r="C24" s="80" t="n">
         <f aca="false">G23</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D24" s="81" t="n">
+      <c r="D24" s="80" t="n">
         <f aca="false">IF(A24&gt;$C$6,MIN(C24,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="81" t="n">
+      <c r="E24" s="80" t="n">
         <f aca="false">C24*$C$8*DAY(B24)/$C$11</f>
         <v>249572.728642172</v>
       </c>
-      <c r="F24" s="81" t="n">
+      <c r="F24" s="80" t="n">
         <f aca="false">D24+E24</f>
         <v>249572.728642172</v>
       </c>
-      <c r="G24" s="81" t="n">
+      <c r="G24" s="80" t="n">
         <f aca="false">C24-D24</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H24" s="76" t="n">
+      <c r="H24" s="94" t="n">
         <f aca="false">YEAR(B24)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="76" t="n">
+      <c r="A25" s="94" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="95" t="n">
         <f aca="false">EOMONTH($C$10,9)</f>
         <v>46691</v>
       </c>
-      <c r="C25" s="81" t="n">
+      <c r="C25" s="80" t="n">
         <f aca="false">G24</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D25" s="81" t="n">
+      <c r="D25" s="80" t="n">
         <f aca="false">IF(A25&gt;$C$6,MIN(C25,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="81" t="n">
+      <c r="E25" s="80" t="n">
         <f aca="false">C25*$C$8*DAY(B25)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F25" s="81" t="n">
+      <c r="F25" s="80" t="n">
         <f aca="false">D25+E25</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G25" s="81" t="n">
+      <c r="G25" s="80" t="n">
         <f aca="false">C25-D25</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H25" s="76" t="n">
+      <c r="H25" s="94" t="n">
         <f aca="false">YEAR(B25)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76" t="n">
+      <c r="A26" s="94" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="95" t="n">
         <f aca="false">EOMONTH($C$10,10)</f>
         <v>46721</v>
       </c>
-      <c r="C26" s="81" t="n">
+      <c r="C26" s="80" t="n">
         <f aca="false">G25</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D26" s="81" t="n">
+      <c r="D26" s="80" t="n">
         <f aca="false">IF(A26&gt;$C$6,MIN(C26,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="81" t="n">
+      <c r="E26" s="80" t="n">
         <f aca="false">C26*$C$8*DAY(B26)/$C$11</f>
         <v>249572.728642172</v>
       </c>
-      <c r="F26" s="81" t="n">
+      <c r="F26" s="80" t="n">
         <f aca="false">D26+E26</f>
         <v>249572.728642172</v>
       </c>
-      <c r="G26" s="81" t="n">
+      <c r="G26" s="80" t="n">
         <f aca="false">C26-D26</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H26" s="76" t="n">
+      <c r="H26" s="94" t="n">
         <f aca="false">YEAR(B26)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="76" t="n">
+      <c r="A27" s="94" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="95" t="n">
         <f aca="false">EOMONTH($C$10,11)</f>
         <v>46752</v>
       </c>
-      <c r="C27" s="81" t="n">
+      <c r="C27" s="80" t="n">
         <f aca="false">G26</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D27" s="81" t="n">
+      <c r="D27" s="80" t="n">
         <f aca="false">IF(A27&gt;$C$6,MIN(C27,$C$13),0)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="81" t="n">
+      <c r="E27" s="80" t="n">
         <f aca="false">C27*$C$8*DAY(B27)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F27" s="81" t="n">
+      <c r="F27" s="80" t="n">
         <f aca="false">D27+E27</f>
         <v>257891.819596911</v>
       </c>
-      <c r="G27" s="81" t="n">
+      <c r="G27" s="80" t="n">
         <f aca="false">C27-D27</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="H27" s="76" t="n">
+      <c r="H27" s="94" t="n">
         <f aca="false">YEAR(B27)-YEAR($C$10)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="76" t="n">
+      <c r="A28" s="94" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="95" t="n">
         <f aca="false">EOMONTH($C$10,12)</f>
         <v>46783</v>
       </c>
-      <c r="C28" s="81" t="n">
+      <c r="C28" s="80" t="n">
         <f aca="false">G27</f>
         <v>42783896.3386581</v>
       </c>
-      <c r="D28" s="81" t="n">
+      <c r="D28" s="80" t="n">
         <f aca="false">IF(A28&gt;$C$6,MIN(C28,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E28" s="81" t="n">
+      <c r="E28" s="80" t="n">
         <f aca="false">C28*$C$8*DAY(B28)/$C$11</f>
         <v>257891.819596911</v>
       </c>
-      <c r="F28" s="81" t="n">
+      <c r="F28" s="80" t="n">
         <f aca="false">D28+E28</f>
         <v>852112.602078273</v>
       </c>
-      <c r="G28" s="81" t="n">
+      <c r="G28" s="80" t="n">
         <f aca="false">C28-D28</f>
         <v>42189675.5561767</v>
       </c>
-      <c r="H28" s="76" t="n">
+      <c r="H28" s="94" t="n">
         <f aca="false">YEAR(B28)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="76" t="n">
+      <c r="A29" s="94" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="95" t="n">
         <f aca="false">EOMONTH($C$10,13)</f>
         <v>46812</v>
       </c>
-      <c r="C29" s="81" t="n">
+      <c r="C29" s="80" t="n">
         <f aca="false">G28</f>
         <v>42189675.5561767</v>
       </c>
-      <c r="D29" s="81" t="n">
+      <c r="D29" s="80" t="n">
         <f aca="false">IF(A29&gt;$C$6,MIN(C29,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E29" s="81" t="n">
+      <c r="E29" s="80" t="n">
         <f aca="false">C29*$C$8*DAY(B29)/$C$11</f>
         <v>237902.892719552</v>
       </c>
-      <c r="F29" s="81" t="n">
+      <c r="F29" s="80" t="n">
         <f aca="false">D29+E29</f>
         <v>832123.675200914</v>
       </c>
-      <c r="G29" s="81" t="n">
+      <c r="G29" s="80" t="n">
         <f aca="false">C29-D29</f>
         <v>41595454.7736954</v>
       </c>
-      <c r="H29" s="76" t="n">
+      <c r="H29" s="94" t="n">
         <f aca="false">YEAR(B29)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="76" t="n">
+      <c r="A30" s="94" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="95" t="n">
         <f aca="false">EOMONTH($C$10,14)</f>
         <v>46843</v>
       </c>
-      <c r="C30" s="81" t="n">
+      <c r="C30" s="80" t="n">
         <f aca="false">G29</f>
         <v>41595454.7736954</v>
       </c>
-      <c r="D30" s="81" t="n">
+      <c r="D30" s="80" t="n">
         <f aca="false">IF(A30&gt;$C$6,MIN(C30,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E30" s="81" t="n">
+      <c r="E30" s="80" t="n">
         <f aca="false">C30*$C$8*DAY(B30)/$C$11</f>
         <v>250728.157941441</v>
       </c>
-      <c r="F30" s="81" t="n">
+      <c r="F30" s="80" t="n">
         <f aca="false">D30+E30</f>
         <v>844948.940422804</v>
       </c>
-      <c r="G30" s="81" t="n">
+      <c r="G30" s="80" t="n">
         <f aca="false">C30-D30</f>
         <v>41001233.991214</v>
       </c>
-      <c r="H30" s="76" t="n">
+      <c r="H30" s="94" t="n">
         <f aca="false">YEAR(B30)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="76" t="n">
+      <c r="A31" s="94" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="95" t="n">
         <f aca="false">EOMONTH($C$10,15)</f>
         <v>46873</v>
       </c>
-      <c r="C31" s="81" t="n">
+      <c r="C31" s="80" t="n">
         <f aca="false">G30</f>
         <v>41001233.991214</v>
       </c>
-      <c r="D31" s="81" t="n">
+      <c r="D31" s="80" t="n">
         <f aca="false">IF(A31&gt;$C$6,MIN(C31,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E31" s="81" t="n">
+      <c r="E31" s="80" t="n">
         <f aca="false">C31*$C$8*DAY(B31)/$C$11</f>
         <v>239173.864948748</v>
       </c>
-      <c r="F31" s="81" t="n">
+      <c r="F31" s="80" t="n">
         <f aca="false">D31+E31</f>
         <v>833394.647430111</v>
       </c>
-      <c r="G31" s="81" t="n">
+      <c r="G31" s="80" t="n">
         <f aca="false">C31-D31</f>
         <v>40407013.2087326</v>
       </c>
-      <c r="H31" s="76" t="n">
+      <c r="H31" s="94" t="n">
         <f aca="false">YEAR(B31)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="76" t="n">
+      <c r="A32" s="94" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="95" t="n">
         <f aca="false">EOMONTH($C$10,16)</f>
         <v>46904</v>
       </c>
-      <c r="C32" s="81" t="n">
+      <c r="C32" s="80" t="n">
         <f aca="false">G31</f>
         <v>40407013.2087326</v>
       </c>
-      <c r="D32" s="81" t="n">
+      <c r="D32" s="80" t="n">
         <f aca="false">IF(A32&gt;$C$6,MIN(C32,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E32" s="81" t="n">
+      <c r="E32" s="80" t="n">
         <f aca="false">C32*$C$8*DAY(B32)/$C$11</f>
         <v>243564.496285972</v>
       </c>
-      <c r="F32" s="81" t="n">
+      <c r="F32" s="80" t="n">
         <f aca="false">D32+E32</f>
         <v>837785.278767334</v>
       </c>
-      <c r="G32" s="81" t="n">
+      <c r="G32" s="80" t="n">
         <f aca="false">C32-D32</f>
         <v>39812792.4262513</v>
       </c>
-      <c r="H32" s="76" t="n">
+      <c r="H32" s="94" t="n">
         <f aca="false">YEAR(B32)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="76" t="n">
+      <c r="A33" s="94" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="95" t="n">
         <f aca="false">EOMONTH($C$10,17)</f>
         <v>46934</v>
       </c>
-      <c r="C33" s="81" t="n">
+      <c r="C33" s="80" t="n">
         <f aca="false">G32</f>
         <v>39812792.4262513</v>
       </c>
-      <c r="D33" s="81" t="n">
+      <c r="D33" s="80" t="n">
         <f aca="false">IF(A33&gt;$C$6,MIN(C33,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E33" s="81" t="n">
+      <c r="E33" s="80" t="n">
         <f aca="false">C33*$C$8*DAY(B33)/$C$11</f>
         <v>232241.289153132</v>
       </c>
-      <c r="F33" s="81" t="n">
+      <c r="F33" s="80" t="n">
         <f aca="false">D33+E33</f>
         <v>826462.071634495</v>
       </c>
-      <c r="G33" s="81" t="n">
+      <c r="G33" s="80" t="n">
         <f aca="false">C33-D33</f>
         <v>39218571.6437699</v>
       </c>
-      <c r="H33" s="76" t="n">
+      <c r="H33" s="94" t="n">
         <f aca="false">YEAR(B33)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="76" t="n">
+      <c r="A34" s="94" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="95" t="n">
         <f aca="false">EOMONTH($C$10,18)</f>
         <v>46965</v>
       </c>
-      <c r="C34" s="81" t="n">
+      <c r="C34" s="80" t="n">
         <f aca="false">G33</f>
         <v>39218571.6437699</v>
       </c>
-      <c r="D34" s="81" t="n">
+      <c r="D34" s="80" t="n">
         <f aca="false">IF(A34&gt;$C$6,MIN(C34,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E34" s="81" t="n">
+      <c r="E34" s="80" t="n">
         <f aca="false">C34*$C$8*DAY(B34)/$C$11</f>
         <v>236400.834630502</v>
       </c>
-      <c r="F34" s="81" t="n">
+      <c r="F34" s="80" t="n">
         <f aca="false">D34+E34</f>
         <v>830621.617111864</v>
       </c>
-      <c r="G34" s="81" t="n">
+      <c r="G34" s="80" t="n">
         <f aca="false">C34-D34</f>
         <v>38624350.8612885</v>
       </c>
-      <c r="H34" s="76" t="n">
+      <c r="H34" s="94" t="n">
         <f aca="false">YEAR(B34)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="76" t="n">
+      <c r="A35" s="94" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="95" t="n">
         <f aca="false">EOMONTH($C$10,19)</f>
         <v>46996</v>
       </c>
-      <c r="C35" s="81" t="n">
+      <c r="C35" s="80" t="n">
         <f aca="false">G34</f>
         <v>38624350.8612885</v>
       </c>
-      <c r="D35" s="81" t="n">
+      <c r="D35" s="80" t="n">
         <f aca="false">IF(A35&gt;$C$6,MIN(C35,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E35" s="81" t="n">
+      <c r="E35" s="80" t="n">
         <f aca="false">C35*$C$8*DAY(B35)/$C$11</f>
         <v>232819.003802767</v>
       </c>
-      <c r="F35" s="81" t="n">
+      <c r="F35" s="80" t="n">
         <f aca="false">D35+E35</f>
         <v>827039.786284129</v>
       </c>
-      <c r="G35" s="81" t="n">
+      <c r="G35" s="80" t="n">
         <f aca="false">C35-D35</f>
         <v>38030130.0788072</v>
       </c>
-      <c r="H35" s="76" t="n">
+      <c r="H35" s="94" t="n">
         <f aca="false">YEAR(B35)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="76" t="n">
+      <c r="A36" s="94" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="95" t="n">
         <f aca="false">EOMONTH($C$10,20)</f>
         <v>47026</v>
       </c>
-      <c r="C36" s="81" t="n">
+      <c r="C36" s="80" t="n">
         <f aca="false">G35</f>
         <v>38030130.0788072</v>
       </c>
-      <c r="D36" s="81" t="n">
+      <c r="D36" s="80" t="n">
         <f aca="false">IF(A36&gt;$C$6,MIN(C36,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E36" s="81" t="n">
+      <c r="E36" s="80" t="n">
         <f aca="false">C36*$C$8*DAY(B36)/$C$11</f>
         <v>221842.425459709</v>
       </c>
-      <c r="F36" s="81" t="n">
+      <c r="F36" s="80" t="n">
         <f aca="false">D36+E36</f>
         <v>816063.207941071</v>
       </c>
-      <c r="G36" s="81" t="n">
+      <c r="G36" s="80" t="n">
         <f aca="false">C36-D36</f>
         <v>37435909.2963258</v>
       </c>
-      <c r="H36" s="76" t="n">
+      <c r="H36" s="94" t="n">
         <f aca="false">YEAR(B36)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="76" t="n">
+      <c r="A37" s="94" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="95" t="n">
         <f aca="false">EOMONTH($C$10,21)</f>
         <v>47057</v>
       </c>
-      <c r="C37" s="81" t="n">
+      <c r="C37" s="80" t="n">
         <f aca="false">G36</f>
         <v>37435909.2963258</v>
       </c>
-      <c r="D37" s="81" t="n">
+      <c r="D37" s="80" t="n">
         <f aca="false">IF(A37&gt;$C$6,MIN(C37,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E37" s="81" t="n">
+      <c r="E37" s="80" t="n">
         <f aca="false">C37*$C$8*DAY(B37)/$C$11</f>
         <v>225655.342147297</v>
       </c>
-      <c r="F37" s="81" t="n">
+      <c r="F37" s="80" t="n">
         <f aca="false">D37+E37</f>
         <v>819876.12462866</v>
       </c>
-      <c r="G37" s="81" t="n">
+      <c r="G37" s="80" t="n">
         <f aca="false">C37-D37</f>
         <v>36841688.5138444</v>
       </c>
-      <c r="H37" s="76" t="n">
+      <c r="H37" s="94" t="n">
         <f aca="false">YEAR(B37)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="76" t="n">
+      <c r="A38" s="94" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="95" t="n">
         <f aca="false">EOMONTH($C$10,22)</f>
         <v>47087</v>
       </c>
-      <c r="C38" s="81" t="n">
+      <c r="C38" s="80" t="n">
         <f aca="false">G37</f>
         <v>36841688.5138444</v>
       </c>
-      <c r="D38" s="81" t="n">
+      <c r="D38" s="80" t="n">
         <f aca="false">IF(A38&gt;$C$6,MIN(C38,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E38" s="81" t="n">
+      <c r="E38" s="80" t="n">
         <f aca="false">C38*$C$8*DAY(B38)/$C$11</f>
         <v>214909.849664093</v>
       </c>
-      <c r="F38" s="81" t="n">
+      <c r="F38" s="80" t="n">
         <f aca="false">D38+E38</f>
         <v>809130.632145455</v>
       </c>
-      <c r="G38" s="81" t="n">
+      <c r="G38" s="80" t="n">
         <f aca="false">C38-D38</f>
         <v>36247467.7313631</v>
       </c>
-      <c r="H38" s="76" t="n">
+      <c r="H38" s="94" t="n">
         <f aca="false">YEAR(B38)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="76" t="n">
+      <c r="A39" s="94" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="95" t="n">
         <f aca="false">EOMONTH($C$10,23)</f>
         <v>47118</v>
       </c>
-      <c r="C39" s="81" t="n">
+      <c r="C39" s="80" t="n">
         <f aca="false">G38</f>
         <v>36247467.7313631</v>
       </c>
-      <c r="D39" s="81" t="n">
+      <c r="D39" s="80" t="n">
         <f aca="false">IF(A39&gt;$C$6,MIN(C39,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E39" s="81" t="n">
+      <c r="E39" s="80" t="n">
         <f aca="false">C39*$C$8*DAY(B39)/$C$11</f>
         <v>218491.680491827</v>
       </c>
-      <c r="F39" s="81" t="n">
+      <c r="F39" s="80" t="n">
         <f aca="false">D39+E39</f>
         <v>812712.46297319</v>
       </c>
-      <c r="G39" s="81" t="n">
+      <c r="G39" s="80" t="n">
         <f aca="false">C39-D39</f>
         <v>35653246.9488817</v>
       </c>
-      <c r="H39" s="76" t="n">
+      <c r="H39" s="94" t="n">
         <f aca="false">YEAR(B39)-YEAR($C$10)+1</f>
         <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="76" t="n">
+      <c r="A40" s="94" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="95" t="n">
         <f aca="false">EOMONTH($C$10,24)</f>
         <v>47149</v>
       </c>
-      <c r="C40" s="81" t="n">
+      <c r="C40" s="80" t="n">
         <f aca="false">G39</f>
         <v>35653246.9488817</v>
       </c>
-      <c r="D40" s="81" t="n">
+      <c r="D40" s="80" t="n">
         <f aca="false">IF(A40&gt;$C$6,MIN(C40,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E40" s="81" t="n">
+      <c r="E40" s="80" t="n">
         <f aca="false">C40*$C$8*DAY(B40)/$C$11</f>
         <v>214909.849664093</v>
       </c>
-      <c r="F40" s="81" t="n">
+      <c r="F40" s="80" t="n">
         <f aca="false">D40+E40</f>
         <v>809130.632145455</v>
       </c>
-      <c r="G40" s="81" t="n">
+      <c r="G40" s="80" t="n">
         <f aca="false">C40-D40</f>
         <v>35059026.1664003</v>
       </c>
-      <c r="H40" s="76" t="n">
+      <c r="H40" s="94" t="n">
         <f aca="false">YEAR(B40)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="76" t="n">
+      <c r="A41" s="94" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="95" t="n">
         <f aca="false">EOMONTH($C$10,25)</f>
         <v>47177</v>
       </c>
-      <c r="C41" s="81" t="n">
+      <c r="C41" s="80" t="n">
         <f aca="false">G40</f>
         <v>35059026.1664003</v>
       </c>
-      <c r="D41" s="81" t="n">
+      <c r="D41" s="80" t="n">
         <f aca="false">IF(A41&gt;$C$6,MIN(C41,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E41" s="81" t="n">
+      <c r="E41" s="80" t="n">
         <f aca="false">C41*$C$8*DAY(B41)/$C$11</f>
         <v>190876.920239291</v>
       </c>
-      <c r="F41" s="81" t="n">
+      <c r="F41" s="80" t="n">
         <f aca="false">D41+E41</f>
         <v>785097.702720653</v>
       </c>
-      <c r="G41" s="81" t="n">
+      <c r="G41" s="80" t="n">
         <f aca="false">C41-D41</f>
         <v>34464805.383919</v>
       </c>
-      <c r="H41" s="76" t="n">
+      <c r="H41" s="94" t="n">
         <f aca="false">YEAR(B41)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="76" t="n">
+      <c r="A42" s="94" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="95" t="n">
         <f aca="false">EOMONTH($C$10,26)</f>
         <v>47208</v>
       </c>
-      <c r="C42" s="81" t="n">
+      <c r="C42" s="80" t="n">
         <f aca="false">G41</f>
         <v>34464805.383919</v>
       </c>
-      <c r="D42" s="81" t="n">
+      <c r="D42" s="80" t="n">
         <f aca="false">IF(A42&gt;$C$6,MIN(C42,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E42" s="81" t="n">
+      <c r="E42" s="80" t="n">
         <f aca="false">C42*$C$8*DAY(B42)/$C$11</f>
         <v>207746.188008623</v>
       </c>
-      <c r="F42" s="81" t="n">
+      <c r="F42" s="80" t="n">
         <f aca="false">D42+E42</f>
         <v>801966.970489985</v>
       </c>
-      <c r="G42" s="81" t="n">
+      <c r="G42" s="80" t="n">
         <f aca="false">C42-D42</f>
         <v>33870584.6014376</v>
       </c>
-      <c r="H42" s="76" t="n">
+      <c r="H42" s="94" t="n">
         <f aca="false">YEAR(B42)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="76" t="n">
+      <c r="A43" s="94" t="n">
         <v>28</v>
       </c>
       <c r="B43" s="95" t="n">
         <f aca="false">EOMONTH($C$10,27)</f>
         <v>47238</v>
       </c>
-      <c r="C43" s="81" t="n">
+      <c r="C43" s="80" t="n">
         <f aca="false">G42</f>
         <v>33870584.6014376</v>
       </c>
-      <c r="D43" s="81" t="n">
+      <c r="D43" s="80" t="n">
         <f aca="false">IF(A43&gt;$C$6,MIN(C43,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E43" s="81" t="n">
+      <c r="E43" s="80" t="n">
         <f aca="false">C43*$C$8*DAY(B43)/$C$11</f>
         <v>197578.410175053</v>
       </c>
-      <c r="F43" s="81" t="n">
+      <c r="F43" s="80" t="n">
         <f aca="false">D43+E43</f>
         <v>791799.192656415</v>
       </c>
-      <c r="G43" s="81" t="n">
+      <c r="G43" s="80" t="n">
         <f aca="false">C43-D43</f>
         <v>33276363.8189562</v>
       </c>
-      <c r="H43" s="76" t="n">
+      <c r="H43" s="94" t="n">
         <f aca="false">YEAR(B43)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="76" t="n">
+      <c r="A44" s="94" t="n">
         <v>29</v>
       </c>
       <c r="B44" s="95" t="n">
         <f aca="false">EOMONTH($C$10,28)</f>
         <v>47269</v>
       </c>
-      <c r="C44" s="81" t="n">
+      <c r="C44" s="80" t="n">
         <f aca="false">G43</f>
         <v>33276363.8189562</v>
       </c>
-      <c r="D44" s="81" t="n">
+      <c r="D44" s="80" t="n">
         <f aca="false">IF(A44&gt;$C$6,MIN(C44,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E44" s="81" t="n">
+      <c r="E44" s="80" t="n">
         <f aca="false">C44*$C$8*DAY(B44)/$C$11</f>
         <v>200582.526353153</v>
       </c>
-      <c r="F44" s="81" t="n">
+      <c r="F44" s="80" t="n">
         <f aca="false">D44+E44</f>
         <v>794803.308834515</v>
       </c>
-      <c r="G44" s="81" t="n">
+      <c r="G44" s="80" t="n">
         <f aca="false">C44-D44</f>
         <v>32682143.0364749</v>
       </c>
-      <c r="H44" s="76" t="n">
+      <c r="H44" s="94" t="n">
         <f aca="false">YEAR(B44)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="76" t="n">
+      <c r="A45" s="94" t="n">
         <v>30</v>
       </c>
       <c r="B45" s="95" t="n">
         <f aca="false">EOMONTH($C$10,29)</f>
         <v>47299</v>
       </c>
-      <c r="C45" s="81" t="n">
+      <c r="C45" s="80" t="n">
         <f aca="false">G44</f>
         <v>32682143.0364749</v>
       </c>
-      <c r="D45" s="81" t="n">
+      <c r="D45" s="80" t="n">
         <f aca="false">IF(A45&gt;$C$6,MIN(C45,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E45" s="81" t="n">
+      <c r="E45" s="80" t="n">
         <f aca="false">C45*$C$8*DAY(B45)/$C$11</f>
         <v>190645.834379437</v>
       </c>
-      <c r="F45" s="81" t="n">
+      <c r="F45" s="80" t="n">
         <f aca="false">D45+E45</f>
         <v>784866.616860799</v>
       </c>
-      <c r="G45" s="81" t="n">
+      <c r="G45" s="80" t="n">
         <f aca="false">C45-D45</f>
         <v>32087922.2539935</v>
       </c>
-      <c r="H45" s="76" t="n">
+      <c r="H45" s="94" t="n">
         <f aca="false">YEAR(B45)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="76" t="n">
+      <c r="A46" s="94" t="n">
         <v>31</v>
       </c>
       <c r="B46" s="95" t="n">
         <f aca="false">EOMONTH($C$10,30)</f>
         <v>47330</v>
       </c>
-      <c r="C46" s="81" t="n">
+      <c r="C46" s="80" t="n">
         <f aca="false">G45</f>
         <v>32087922.2539935</v>
       </c>
-      <c r="D46" s="81" t="n">
+      <c r="D46" s="80" t="n">
         <f aca="false">IF(A46&gt;$C$6,MIN(C46,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E46" s="81" t="n">
+      <c r="E46" s="80" t="n">
         <f aca="false">C46*$C$8*DAY(B46)/$C$11</f>
         <v>193418.864697683</v>
       </c>
-      <c r="F46" s="81" t="n">
+      <c r="F46" s="80" t="n">
         <f aca="false">D46+E46</f>
         <v>787639.647179046</v>
       </c>
-      <c r="G46" s="81" t="n">
+      <c r="G46" s="80" t="n">
         <f aca="false">C46-D46</f>
         <v>31493701.4715122</v>
       </c>
-      <c r="H46" s="76" t="n">
+      <c r="H46" s="94" t="n">
         <f aca="false">YEAR(B46)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="76" t="n">
+      <c r="A47" s="94" t="n">
         <v>32</v>
       </c>
       <c r="B47" s="95" t="n">
         <f aca="false">EOMONTH($C$10,31)</f>
         <v>47361</v>
       </c>
-      <c r="C47" s="81" t="n">
+      <c r="C47" s="80" t="n">
         <f aca="false">G46</f>
         <v>31493701.4715122</v>
       </c>
-      <c r="D47" s="81" t="n">
+      <c r="D47" s="80" t="n">
         <f aca="false">IF(A47&gt;$C$6,MIN(C47,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E47" s="81" t="n">
+      <c r="E47" s="80" t="n">
         <f aca="false">C47*$C$8*DAY(B47)/$C$11</f>
         <v>189837.033869948</v>
       </c>
-      <c r="F47" s="81" t="n">
+      <c r="F47" s="80" t="n">
         <f aca="false">D47+E47</f>
         <v>784057.816351311</v>
       </c>
-      <c r="G47" s="81" t="n">
+      <c r="G47" s="80" t="n">
         <f aca="false">C47-D47</f>
         <v>30899480.6890308</v>
       </c>
-      <c r="H47" s="76" t="n">
+      <c r="H47" s="94" t="n">
         <f aca="false">YEAR(B47)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="76" t="n">
+      <c r="A48" s="94" t="n">
         <v>33</v>
       </c>
       <c r="B48" s="95" t="n">
         <f aca="false">EOMONTH($C$10,32)</f>
         <v>47391</v>
       </c>
-      <c r="C48" s="81" t="n">
+      <c r="C48" s="80" t="n">
         <f aca="false">G47</f>
         <v>30899480.6890308</v>
       </c>
-      <c r="D48" s="81" t="n">
+      <c r="D48" s="80" t="n">
         <f aca="false">IF(A48&gt;$C$6,MIN(C48,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E48" s="81" t="n">
+      <c r="E48" s="80" t="n">
         <f aca="false">C48*$C$8*DAY(B48)/$C$11</f>
         <v>180246.970686013</v>
       </c>
-      <c r="F48" s="81" t="n">
+      <c r="F48" s="80" t="n">
         <f aca="false">D48+E48</f>
         <v>774467.753167375</v>
       </c>
-      <c r="G48" s="81" t="n">
+      <c r="G48" s="80" t="n">
         <f aca="false">C48-D48</f>
         <v>30305259.9065494</v>
       </c>
-      <c r="H48" s="76" t="n">
+      <c r="H48" s="94" t="n">
         <f aca="false">YEAR(B48)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="76" t="n">
+      <c r="A49" s="94" t="n">
         <v>34</v>
       </c>
       <c r="B49" s="95" t="n">
         <f aca="false">EOMONTH($C$10,33)</f>
         <v>47422</v>
       </c>
-      <c r="C49" s="81" t="n">
+      <c r="C49" s="80" t="n">
         <f aca="false">G48</f>
         <v>30305259.9065494</v>
       </c>
-      <c r="D49" s="81" t="n">
+      <c r="D49" s="80" t="n">
         <f aca="false">IF(A49&gt;$C$6,MIN(C49,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E49" s="81" t="n">
+      <c r="E49" s="80" t="n">
         <f aca="false">C49*$C$8*DAY(B49)/$C$11</f>
         <v>182673.372214479</v>
       </c>
-      <c r="F49" s="81" t="n">
+      <c r="F49" s="80" t="n">
         <f aca="false">D49+E49</f>
         <v>776894.154695841</v>
       </c>
-      <c r="G49" s="81" t="n">
+      <c r="G49" s="80" t="n">
         <f aca="false">C49-D49</f>
         <v>29711039.1240681</v>
       </c>
-      <c r="H49" s="76" t="n">
+      <c r="H49" s="94" t="n">
         <f aca="false">YEAR(B49)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="76" t="n">
+      <c r="A50" s="94" t="n">
         <v>35</v>
       </c>
       <c r="B50" s="95" t="n">
         <f aca="false">EOMONTH($C$10,34)</f>
         <v>47452</v>
       </c>
-      <c r="C50" s="81" t="n">
+      <c r="C50" s="80" t="n">
         <f aca="false">G49</f>
         <v>29711039.1240681</v>
       </c>
-      <c r="D50" s="81" t="n">
+      <c r="D50" s="80" t="n">
         <f aca="false">IF(A50&gt;$C$6,MIN(C50,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E50" s="81" t="n">
+      <c r="E50" s="80" t="n">
         <f aca="false">C50*$C$8*DAY(B50)/$C$11</f>
         <v>173314.394890397</v>
       </c>
-      <c r="F50" s="81" t="n">
+      <c r="F50" s="80" t="n">
         <f aca="false">D50+E50</f>
         <v>767535.177371759</v>
       </c>
-      <c r="G50" s="81" t="n">
+      <c r="G50" s="80" t="n">
         <f aca="false">C50-D50</f>
         <v>29116818.3415867</v>
       </c>
-      <c r="H50" s="76" t="n">
+      <c r="H50" s="94" t="n">
         <f aca="false">YEAR(B50)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="76" t="n">
+      <c r="A51" s="94" t="n">
         <v>36</v>
       </c>
       <c r="B51" s="95" t="n">
         <f aca="false">EOMONTH($C$10,35)</f>
         <v>47483</v>
       </c>
-      <c r="C51" s="81" t="n">
+      <c r="C51" s="80" t="n">
         <f aca="false">G50</f>
         <v>29116818.3415867</v>
       </c>
-      <c r="D51" s="81" t="n">
+      <c r="D51" s="80" t="n">
         <f aca="false">IF(A51&gt;$C$6,MIN(C51,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E51" s="81" t="n">
+      <c r="E51" s="80" t="n">
         <f aca="false">C51*$C$8*DAY(B51)/$C$11</f>
         <v>175509.710559009</v>
       </c>
-      <c r="F51" s="81" t="n">
+      <c r="F51" s="80" t="n">
         <f aca="false">D51+E51</f>
         <v>769730.493040371</v>
       </c>
-      <c r="G51" s="81" t="n">
+      <c r="G51" s="80" t="n">
         <f aca="false">C51-D51</f>
         <v>28522597.5591054</v>
       </c>
-      <c r="H51" s="76" t="n">
+      <c r="H51" s="94" t="n">
         <f aca="false">YEAR(B51)-YEAR($C$10)+1</f>
         <v>3</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="76" t="n">
+      <c r="A52" s="94" t="n">
         <v>37</v>
       </c>
       <c r="B52" s="95" t="n">
         <f aca="false">EOMONTH($C$10,36)</f>
         <v>47514</v>
       </c>
-      <c r="C52" s="81" t="n">
+      <c r="C52" s="80" t="n">
         <f aca="false">G51</f>
         <v>28522597.5591054</v>
       </c>
-      <c r="D52" s="81" t="n">
+      <c r="D52" s="80" t="n">
         <f aca="false">IF(A52&gt;$C$6,MIN(C52,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E52" s="81" t="n">
+      <c r="E52" s="80" t="n">
         <f aca="false">C52*$C$8*DAY(B52)/$C$11</f>
         <v>171927.879731274</v>
       </c>
-      <c r="F52" s="81" t="n">
+      <c r="F52" s="80" t="n">
         <f aca="false">D52+E52</f>
         <v>766148.662212636</v>
       </c>
-      <c r="G52" s="81" t="n">
+      <c r="G52" s="80" t="n">
         <f aca="false">C52-D52</f>
         <v>27928376.776624</v>
       </c>
-      <c r="H52" s="76" t="n">
+      <c r="H52" s="94" t="n">
         <f aca="false">YEAR(B52)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="76" t="n">
+      <c r="A53" s="94" t="n">
         <v>38</v>
       </c>
       <c r="B53" s="95" t="n">
         <f aca="false">EOMONTH($C$10,37)</f>
         <v>47542</v>
       </c>
-      <c r="C53" s="81" t="n">
+      <c r="C53" s="80" t="n">
         <f aca="false">G52</f>
         <v>27928376.776624</v>
       </c>
-      <c r="D53" s="81" t="n">
+      <c r="D53" s="80" t="n">
         <f aca="false">IF(A53&gt;$C$6,MIN(C53,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E53" s="81" t="n">
+      <c r="E53" s="80" t="n">
         <f aca="false">C53*$C$8*DAY(B53)/$C$11</f>
         <v>152054.495783842</v>
       </c>
-      <c r="F53" s="81" t="n">
+      <c r="F53" s="80" t="n">
         <f aca="false">D53+E53</f>
         <v>746275.278265204</v>
       </c>
-      <c r="G53" s="81" t="n">
+      <c r="G53" s="80" t="n">
         <f aca="false">C53-D53</f>
         <v>27334155.9941426</v>
       </c>
-      <c r="H53" s="76" t="n">
+      <c r="H53" s="94" t="n">
         <f aca="false">YEAR(B53)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="76" t="n">
+      <c r="A54" s="94" t="n">
         <v>39</v>
       </c>
       <c r="B54" s="95" t="n">
         <f aca="false">EOMONTH($C$10,38)</f>
         <v>47573</v>
       </c>
-      <c r="C54" s="81" t="n">
+      <c r="C54" s="80" t="n">
         <f aca="false">G53</f>
         <v>27334155.9941426</v>
       </c>
-      <c r="D54" s="81" t="n">
+      <c r="D54" s="80" t="n">
         <f aca="false">IF(A54&gt;$C$6,MIN(C54,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E54" s="81" t="n">
+      <c r="E54" s="80" t="n">
         <f aca="false">C54*$C$8*DAY(B54)/$C$11</f>
         <v>164764.218075804</v>
       </c>
-      <c r="F54" s="81" t="n">
+      <c r="F54" s="80" t="n">
         <f aca="false">D54+E54</f>
         <v>758985.000557167</v>
       </c>
-      <c r="G54" s="81" t="n">
+      <c r="G54" s="80" t="n">
         <f aca="false">C54-D54</f>
         <v>26739935.2116613</v>
       </c>
-      <c r="H54" s="76" t="n">
+      <c r="H54" s="94" t="n">
         <f aca="false">YEAR(B54)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="76" t="n">
+      <c r="A55" s="94" t="n">
         <v>40</v>
       </c>
       <c r="B55" s="95" t="n">
         <f aca="false">EOMONTH($C$10,39)</f>
         <v>47603</v>
       </c>
-      <c r="C55" s="81" t="n">
+      <c r="C55" s="80" t="n">
         <f aca="false">G54</f>
         <v>26739935.2116613</v>
       </c>
-      <c r="D55" s="81" t="n">
+      <c r="D55" s="80" t="n">
         <f aca="false">IF(A55&gt;$C$6,MIN(C55,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E55" s="81" t="n">
+      <c r="E55" s="80" t="n">
         <f aca="false">C55*$C$8*DAY(B55)/$C$11</f>
         <v>155982.955401357</v>
       </c>
-      <c r="F55" s="81" t="n">
+      <c r="F55" s="80" t="n">
         <f aca="false">D55+E55</f>
         <v>750203.73788272</v>
       </c>
-      <c r="G55" s="81" t="n">
+      <c r="G55" s="80" t="n">
         <f aca="false">C55-D55</f>
         <v>26145714.4291799</v>
       </c>
-      <c r="H55" s="76" t="n">
+      <c r="H55" s="94" t="n">
         <f aca="false">YEAR(B55)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="76" t="n">
+      <c r="A56" s="94" t="n">
         <v>41</v>
       </c>
       <c r="B56" s="95" t="n">
         <f aca="false">EOMONTH($C$10,40)</f>
         <v>47634</v>
       </c>
-      <c r="C56" s="81" t="n">
+      <c r="C56" s="80" t="n">
         <f aca="false">G55</f>
         <v>26145714.4291799</v>
       </c>
-      <c r="D56" s="81" t="n">
+      <c r="D56" s="80" t="n">
         <f aca="false">IF(A56&gt;$C$6,MIN(C56,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E56" s="81" t="n">
+      <c r="E56" s="80" t="n">
         <f aca="false">C56*$C$8*DAY(B56)/$C$11</f>
         <v>157600.556420334</v>
       </c>
-      <c r="F56" s="81" t="n">
+      <c r="F56" s="80" t="n">
         <f aca="false">D56+E56</f>
         <v>751821.338901697</v>
       </c>
-      <c r="G56" s="81" t="n">
+      <c r="G56" s="80" t="n">
         <f aca="false">C56-D56</f>
         <v>25551493.6466986</v>
       </c>
-      <c r="H56" s="76" t="n">
+      <c r="H56" s="94" t="n">
         <f aca="false">YEAR(B56)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="76" t="n">
+      <c r="A57" s="94" t="n">
         <v>42</v>
       </c>
       <c r="B57" s="95" t="n">
         <f aca="false">EOMONTH($C$10,41)</f>
         <v>47664</v>
       </c>
-      <c r="C57" s="81" t="n">
+      <c r="C57" s="80" t="n">
         <f aca="false">G56</f>
         <v>25551493.6466986</v>
       </c>
-      <c r="D57" s="81" t="n">
+      <c r="D57" s="80" t="n">
         <f aca="false">IF(A57&gt;$C$6,MIN(C57,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E57" s="81" t="n">
+      <c r="E57" s="80" t="n">
         <f aca="false">C57*$C$8*DAY(B57)/$C$11</f>
         <v>149050.379605742</v>
       </c>
-      <c r="F57" s="81" t="n">
+      <c r="F57" s="80" t="n">
         <f aca="false">D57+E57</f>
         <v>743271.162087104</v>
       </c>
-      <c r="G57" s="81" t="n">
+      <c r="G57" s="80" t="n">
         <f aca="false">C57-D57</f>
         <v>24957272.8642172</v>
       </c>
-      <c r="H57" s="76" t="n">
+      <c r="H57" s="94" t="n">
         <f aca="false">YEAR(B57)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="76" t="n">
+      <c r="A58" s="94" t="n">
         <v>43</v>
       </c>
       <c r="B58" s="95" t="n">
         <f aca="false">EOMONTH($C$10,42)</f>
         <v>47695</v>
       </c>
-      <c r="C58" s="81" t="n">
+      <c r="C58" s="80" t="n">
         <f aca="false">G57</f>
         <v>24957272.8642172</v>
       </c>
-      <c r="D58" s="81" t="n">
+      <c r="D58" s="80" t="n">
         <f aca="false">IF(A58&gt;$C$6,MIN(C58,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E58" s="81" t="n">
+      <c r="E58" s="80" t="n">
         <f aca="false">C58*$C$8*DAY(B58)/$C$11</f>
         <v>150436.894764865</v>
       </c>
-      <c r="F58" s="81" t="n">
+      <c r="F58" s="80" t="n">
         <f aca="false">D58+E58</f>
         <v>744657.677246227</v>
       </c>
-      <c r="G58" s="81" t="n">
+      <c r="G58" s="80" t="n">
         <f aca="false">C58-D58</f>
         <v>24363052.0817358</v>
       </c>
-      <c r="H58" s="76" t="n">
+      <c r="H58" s="94" t="n">
         <f aca="false">YEAR(B58)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="76" t="n">
+      <c r="A59" s="94" t="n">
         <v>44</v>
       </c>
       <c r="B59" s="95" t="n">
         <f aca="false">EOMONTH($C$10,43)</f>
         <v>47726</v>
       </c>
-      <c r="C59" s="81" t="n">
+      <c r="C59" s="80" t="n">
         <f aca="false">G58</f>
         <v>24363052.0817358</v>
       </c>
-      <c r="D59" s="81" t="n">
+      <c r="D59" s="80" t="n">
         <f aca="false">IF(A59&gt;$C$6,MIN(C59,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E59" s="81" t="n">
+      <c r="E59" s="80" t="n">
         <f aca="false">C59*$C$8*DAY(B59)/$C$11</f>
         <v>146855.06393713</v>
       </c>
-      <c r="F59" s="81" t="n">
+      <c r="F59" s="80" t="n">
         <f aca="false">D59+E59</f>
         <v>741075.846418492</v>
       </c>
-      <c r="G59" s="81" t="n">
+      <c r="G59" s="80" t="n">
         <f aca="false">C59-D59</f>
         <v>23768831.2992545</v>
       </c>
-      <c r="H59" s="76" t="n">
+      <c r="H59" s="94" t="n">
         <f aca="false">YEAR(B59)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="76" t="n">
+      <c r="A60" s="94" t="n">
         <v>45</v>
       </c>
       <c r="B60" s="95" t="n">
         <f aca="false">EOMONTH($C$10,44)</f>
         <v>47756</v>
       </c>
-      <c r="C60" s="81" t="n">
+      <c r="C60" s="80" t="n">
         <f aca="false">G59</f>
         <v>23768831.2992545</v>
       </c>
-      <c r="D60" s="81" t="n">
+      <c r="D60" s="80" t="n">
         <f aca="false">IF(A60&gt;$C$6,MIN(C60,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E60" s="81" t="n">
+      <c r="E60" s="80" t="n">
         <f aca="false">C60*$C$8*DAY(B60)/$C$11</f>
         <v>138651.515912318</v>
       </c>
-      <c r="F60" s="81" t="n">
+      <c r="F60" s="80" t="n">
         <f aca="false">D60+E60</f>
         <v>732872.29839368</v>
       </c>
-      <c r="G60" s="81" t="n">
+      <c r="G60" s="80" t="n">
         <f aca="false">C60-D60</f>
         <v>23174610.5167731</v>
       </c>
-      <c r="H60" s="76" t="n">
+      <c r="H60" s="94" t="n">
         <f aca="false">YEAR(B60)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="76" t="n">
+      <c r="A61" s="94" t="n">
         <v>46</v>
       </c>
       <c r="B61" s="95" t="n">
         <f aca="false">EOMONTH($C$10,45)</f>
         <v>47787</v>
       </c>
-      <c r="C61" s="81" t="n">
+      <c r="C61" s="80" t="n">
         <f aca="false">G60</f>
         <v>23174610.5167731</v>
       </c>
-      <c r="D61" s="81" t="n">
+      <c r="D61" s="80" t="n">
         <f aca="false">IF(A61&gt;$C$6,MIN(C61,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E61" s="81" t="n">
+      <c r="E61" s="80" t="n">
         <f aca="false">C61*$C$8*DAY(B61)/$C$11</f>
         <v>139691.40228166</v>
       </c>
-      <c r="F61" s="81" t="n">
+      <c r="F61" s="80" t="n">
         <f aca="false">D61+E61</f>
         <v>733912.184763022</v>
       </c>
-      <c r="G61" s="81" t="n">
+      <c r="G61" s="80" t="n">
         <f aca="false">C61-D61</f>
         <v>22580389.7342917</v>
       </c>
-      <c r="H61" s="76" t="n">
+      <c r="H61" s="94" t="n">
         <f aca="false">YEAR(B61)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="76" t="n">
+      <c r="A62" s="94" t="n">
         <v>47</v>
       </c>
       <c r="B62" s="95" t="n">
         <f aca="false">EOMONTH($C$10,46)</f>
         <v>47817</v>
       </c>
-      <c r="C62" s="81" t="n">
+      <c r="C62" s="80" t="n">
         <f aca="false">G61</f>
         <v>22580389.7342917</v>
       </c>
-      <c r="D62" s="81" t="n">
+      <c r="D62" s="80" t="n">
         <f aca="false">IF(A62&gt;$C$6,MIN(C62,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E62" s="81" t="n">
+      <c r="E62" s="80" t="n">
         <f aca="false">C62*$C$8*DAY(B62)/$C$11</f>
         <v>131718.940116702</v>
       </c>
-      <c r="F62" s="81" t="n">
+      <c r="F62" s="80" t="n">
         <f aca="false">D62+E62</f>
         <v>725939.722598064</v>
       </c>
-      <c r="G62" s="81" t="n">
+      <c r="G62" s="80" t="n">
         <f aca="false">C62-D62</f>
         <v>21986168.9518104</v>
       </c>
-      <c r="H62" s="76" t="n">
+      <c r="H62" s="94" t="n">
         <f aca="false">YEAR(B62)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="76" t="n">
+      <c r="A63" s="94" t="n">
         <v>48</v>
       </c>
       <c r="B63" s="95" t="n">
         <f aca="false">EOMONTH($C$10,47)</f>
         <v>47848</v>
       </c>
-      <c r="C63" s="81" t="n">
+      <c r="C63" s="80" t="n">
         <f aca="false">G62</f>
         <v>21986168.9518104</v>
       </c>
-      <c r="D63" s="81" t="n">
+      <c r="D63" s="80" t="n">
         <f aca="false">IF(A63&gt;$C$6,MIN(C63,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E63" s="81" t="n">
+      <c r="E63" s="80" t="n">
         <f aca="false">C63*$C$8*DAY(B63)/$C$11</f>
         <v>132527.74062619</v>
       </c>
-      <c r="F63" s="81" t="n">
+      <c r="F63" s="80" t="n">
         <f aca="false">D63+E63</f>
         <v>726748.523107553</v>
       </c>
-      <c r="G63" s="81" t="n">
+      <c r="G63" s="80" t="n">
         <f aca="false">C63-D63</f>
         <v>21391948.169329</v>
       </c>
-      <c r="H63" s="76" t="n">
+      <c r="H63" s="94" t="n">
         <f aca="false">YEAR(B63)-YEAR($C$10)+1</f>
         <v>4</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="76" t="n">
+      <c r="A64" s="94" t="n">
         <v>49</v>
       </c>
       <c r="B64" s="95" t="n">
         <f aca="false">EOMONTH($C$10,48)</f>
         <v>47879</v>
       </c>
-      <c r="C64" s="81" t="n">
+      <c r="C64" s="80" t="n">
         <f aca="false">G63</f>
         <v>21391948.169329</v>
       </c>
-      <c r="D64" s="81" t="n">
+      <c r="D64" s="80" t="n">
         <f aca="false">IF(A64&gt;$C$6,MIN(C64,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E64" s="81" t="n">
+      <c r="E64" s="80" t="n">
         <f aca="false">C64*$C$8*DAY(B64)/$C$11</f>
         <v>128945.909798456</v>
       </c>
-      <c r="F64" s="81" t="n">
+      <c r="F64" s="80" t="n">
         <f aca="false">D64+E64</f>
         <v>723166.692279818</v>
       </c>
-      <c r="G64" s="81" t="n">
+      <c r="G64" s="80" t="n">
         <f aca="false">C64-D64</f>
         <v>20797727.3868477</v>
       </c>
-      <c r="H64" s="76" t="n">
+      <c r="H64" s="94" t="n">
         <f aca="false">YEAR(B64)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="76" t="n">
+      <c r="A65" s="94" t="n">
         <v>50</v>
       </c>
       <c r="B65" s="95" t="n">
         <f aca="false">EOMONTH($C$10,49)</f>
         <v>47907</v>
       </c>
-      <c r="C65" s="81" t="n">
+      <c r="C65" s="80" t="n">
         <f aca="false">G64</f>
         <v>20797727.3868477</v>
       </c>
-      <c r="D65" s="81" t="n">
+      <c r="D65" s="80" t="n">
         <f aca="false">IF(A65&gt;$C$6,MIN(C65,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E65" s="81" t="n">
+      <c r="E65" s="80" t="n">
         <f aca="false">C65*$C$8*DAY(B65)/$C$11</f>
         <v>113232.071328393</v>
       </c>
-      <c r="F65" s="81" t="n">
+      <c r="F65" s="80" t="n">
         <f aca="false">D65+E65</f>
         <v>707452.853809755</v>
       </c>
-      <c r="G65" s="81" t="n">
+      <c r="G65" s="80" t="n">
         <f aca="false">C65-D65</f>
         <v>20203506.6043663</v>
       </c>
-      <c r="H65" s="76" t="n">
+      <c r="H65" s="94" t="n">
         <f aca="false">YEAR(B65)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="76" t="n">
+      <c r="A66" s="94" t="n">
         <v>51</v>
       </c>
       <c r="B66" s="95" t="n">
         <f aca="false">EOMONTH($C$10,50)</f>
         <v>47938</v>
       </c>
-      <c r="C66" s="81" t="n">
+      <c r="C66" s="80" t="n">
         <f aca="false">G65</f>
         <v>20203506.6043663</v>
       </c>
-      <c r="D66" s="81" t="n">
+      <c r="D66" s="80" t="n">
         <f aca="false">IF(A66&gt;$C$6,MIN(C66,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E66" s="81" t="n">
+      <c r="E66" s="80" t="n">
         <f aca="false">C66*$C$8*DAY(B66)/$C$11</f>
         <v>121782.248142986</v>
       </c>
-      <c r="F66" s="81" t="n">
+      <c r="F66" s="80" t="n">
         <f aca="false">D66+E66</f>
         <v>716003.030624348</v>
       </c>
-      <c r="G66" s="81" t="n">
+      <c r="G66" s="80" t="n">
         <f aca="false">C66-D66</f>
         <v>19609285.8218849</v>
       </c>
-      <c r="H66" s="76" t="n">
+      <c r="H66" s="94" t="n">
         <f aca="false">YEAR(B66)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="76" t="n">
+      <c r="A67" s="94" t="n">
         <v>52</v>
       </c>
       <c r="B67" s="95" t="n">
         <f aca="false">EOMONTH($C$10,51)</f>
         <v>47968</v>
       </c>
-      <c r="C67" s="81" t="n">
+      <c r="C67" s="80" t="n">
         <f aca="false">G66</f>
         <v>19609285.8218849</v>
       </c>
-      <c r="D67" s="81" t="n">
+      <c r="D67" s="80" t="n">
         <f aca="false">IF(A67&gt;$C$6,MIN(C67,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E67" s="81" t="n">
+      <c r="E67" s="80" t="n">
         <f aca="false">C67*$C$8*DAY(B67)/$C$11</f>
         <v>114387.500627662</v>
       </c>
-      <c r="F67" s="81" t="n">
+      <c r="F67" s="80" t="n">
         <f aca="false">D67+E67</f>
         <v>708608.283109024</v>
       </c>
-      <c r="G67" s="81" t="n">
+      <c r="G67" s="80" t="n">
         <f aca="false">C67-D67</f>
         <v>19015065.0394036</v>
       </c>
-      <c r="H67" s="76" t="n">
+      <c r="H67" s="94" t="n">
         <f aca="false">YEAR(B67)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="76" t="n">
+      <c r="A68" s="94" t="n">
         <v>53</v>
       </c>
       <c r="B68" s="95" t="n">
         <f aca="false">EOMONTH($C$10,52)</f>
         <v>47999</v>
       </c>
-      <c r="C68" s="81" t="n">
+      <c r="C68" s="80" t="n">
         <f aca="false">G67</f>
         <v>19015065.0394036</v>
       </c>
-      <c r="D68" s="81" t="n">
+      <c r="D68" s="80" t="n">
         <f aca="false">IF(A68&gt;$C$6,MIN(C68,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E68" s="81" t="n">
+      <c r="E68" s="80" t="n">
         <f aca="false">C68*$C$8*DAY(B68)/$C$11</f>
         <v>114618.586487516</v>
       </c>
-      <c r="F68" s="81" t="n">
+      <c r="F68" s="80" t="n">
         <f aca="false">D68+E68</f>
         <v>708839.368968878</v>
       </c>
-      <c r="G68" s="81" t="n">
+      <c r="G68" s="80" t="n">
         <f aca="false">C68-D68</f>
         <v>18420844.2569222</v>
       </c>
-      <c r="H68" s="76" t="n">
+      <c r="H68" s="94" t="n">
         <f aca="false">YEAR(B68)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="76" t="n">
+      <c r="A69" s="94" t="n">
         <v>54</v>
       </c>
       <c r="B69" s="95" t="n">
         <f aca="false">EOMONTH($C$10,53)</f>
         <v>48029</v>
       </c>
-      <c r="C69" s="81" t="n">
+      <c r="C69" s="80" t="n">
         <f aca="false">G68</f>
         <v>18420844.2569222</v>
       </c>
-      <c r="D69" s="81" t="n">
+      <c r="D69" s="80" t="n">
         <f aca="false">IF(A69&gt;$C$6,MIN(C69,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E69" s="81" t="n">
+      <c r="E69" s="80" t="n">
         <f aca="false">C69*$C$8*DAY(B69)/$C$11</f>
         <v>107454.924832046</v>
       </c>
-      <c r="F69" s="81" t="n">
+      <c r="F69" s="80" t="n">
         <f aca="false">D69+E69</f>
         <v>701675.707313409</v>
       </c>
-      <c r="G69" s="81" t="n">
+      <c r="G69" s="80" t="n">
         <f aca="false">C69-D69</f>
         <v>17826623.4744409</v>
       </c>
-      <c r="H69" s="76" t="n">
+      <c r="H69" s="94" t="n">
         <f aca="false">YEAR(B69)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="76" t="n">
+      <c r="A70" s="94" t="n">
         <v>55</v>
       </c>
       <c r="B70" s="95" t="n">
         <f aca="false">EOMONTH($C$10,54)</f>
         <v>48060</v>
       </c>
-      <c r="C70" s="81" t="n">
+      <c r="C70" s="80" t="n">
         <f aca="false">G69</f>
         <v>17826623.4744409</v>
       </c>
-      <c r="D70" s="81" t="n">
+      <c r="D70" s="80" t="n">
         <f aca="false">IF(A70&gt;$C$6,MIN(C70,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E70" s="81" t="n">
+      <c r="E70" s="80" t="n">
         <f aca="false">C70*$C$8*DAY(B70)/$C$11</f>
         <v>107454.924832046</v>
       </c>
-      <c r="F70" s="81" t="n">
+      <c r="F70" s="80" t="n">
         <f aca="false">D70+E70</f>
         <v>701675.707313409</v>
       </c>
-      <c r="G70" s="81" t="n">
+      <c r="G70" s="80" t="n">
         <f aca="false">C70-D70</f>
         <v>17232402.6919595</v>
       </c>
-      <c r="H70" s="76" t="n">
+      <c r="H70" s="94" t="n">
         <f aca="false">YEAR(B70)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="76" t="n">
+      <c r="A71" s="94" t="n">
         <v>56</v>
       </c>
       <c r="B71" s="95" t="n">
         <f aca="false">EOMONTH($C$10,55)</f>
         <v>48091</v>
       </c>
-      <c r="C71" s="81" t="n">
+      <c r="C71" s="80" t="n">
         <f aca="false">G70</f>
         <v>17232402.6919595</v>
       </c>
-      <c r="D71" s="81" t="n">
+      <c r="D71" s="80" t="n">
         <f aca="false">IF(A71&gt;$C$6,MIN(C71,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E71" s="81" t="n">
+      <c r="E71" s="80" t="n">
         <f aca="false">C71*$C$8*DAY(B71)/$C$11</f>
         <v>103873.094004311</v>
       </c>
-      <c r="F71" s="81" t="n">
+      <c r="F71" s="80" t="n">
         <f aca="false">D71+E71</f>
         <v>698093.876485674</v>
       </c>
-      <c r="G71" s="81" t="n">
+      <c r="G71" s="80" t="n">
         <f aca="false">C71-D71</f>
         <v>16638181.9094781</v>
       </c>
-      <c r="H71" s="76" t="n">
+      <c r="H71" s="94" t="n">
         <f aca="false">YEAR(B71)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="76" t="n">
+      <c r="A72" s="94" t="n">
         <v>57</v>
       </c>
       <c r="B72" s="95" t="n">
         <f aca="false">EOMONTH($C$10,56)</f>
         <v>48121</v>
       </c>
-      <c r="C72" s="81" t="n">
+      <c r="C72" s="80" t="n">
         <f aca="false">G71</f>
         <v>16638181.9094781</v>
       </c>
-      <c r="D72" s="81" t="n">
+      <c r="D72" s="80" t="n">
         <f aca="false">IF(A72&gt;$C$6,MIN(C72,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E72" s="81" t="n">
+      <c r="E72" s="80" t="n">
         <f aca="false">C72*$C$8*DAY(B72)/$C$11</f>
         <v>97056.0611386224</v>
       </c>
-      <c r="F72" s="81" t="n">
+      <c r="F72" s="80" t="n">
         <f aca="false">D72+E72</f>
         <v>691276.843619985</v>
       </c>
-      <c r="G72" s="81" t="n">
+      <c r="G72" s="80" t="n">
         <f aca="false">C72-D72</f>
         <v>16043961.1269968</v>
       </c>
-      <c r="H72" s="76" t="n">
+      <c r="H72" s="94" t="n">
         <f aca="false">YEAR(B72)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="76" t="n">
+      <c r="A73" s="94" t="n">
         <v>58</v>
       </c>
       <c r="B73" s="95" t="n">
         <f aca="false">EOMONTH($C$10,57)</f>
         <v>48152</v>
       </c>
-      <c r="C73" s="81" t="n">
+      <c r="C73" s="80" t="n">
         <f aca="false">G72</f>
         <v>16043961.1269968</v>
       </c>
-      <c r="D73" s="81" t="n">
+      <c r="D73" s="80" t="n">
         <f aca="false">IF(A73&gt;$C$6,MIN(C73,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E73" s="81" t="n">
+      <c r="E73" s="80" t="n">
         <f aca="false">C73*$C$8*DAY(B73)/$C$11</f>
         <v>96709.4323488416</v>
       </c>
-      <c r="F73" s="81" t="n">
+      <c r="F73" s="80" t="n">
         <f aca="false">D73+E73</f>
         <v>690930.214830204</v>
       </c>
-      <c r="G73" s="81" t="n">
+      <c r="G73" s="80" t="n">
         <f aca="false">C73-D73</f>
         <v>15449740.3445154</v>
       </c>
-      <c r="H73" s="76" t="n">
+      <c r="H73" s="94" t="n">
         <f aca="false">YEAR(B73)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="76" t="n">
+      <c r="A74" s="94" t="n">
         <v>59</v>
       </c>
       <c r="B74" s="95" t="n">
         <f aca="false">EOMONTH($C$10,58)</f>
         <v>48182</v>
       </c>
-      <c r="C74" s="81" t="n">
+      <c r="C74" s="80" t="n">
         <f aca="false">G73</f>
         <v>15449740.3445154</v>
       </c>
-      <c r="D74" s="81" t="n">
+      <c r="D74" s="80" t="n">
         <f aca="false">IF(A74&gt;$C$6,MIN(C74,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E74" s="81" t="n">
+      <c r="E74" s="80" t="n">
         <f aca="false">C74*$C$8*DAY(B74)/$C$11</f>
         <v>90123.4853430065</v>
       </c>
-      <c r="F74" s="81" t="n">
+      <c r="F74" s="80" t="n">
         <f aca="false">D74+E74</f>
         <v>684344.267824369</v>
       </c>
-      <c r="G74" s="81" t="n">
+      <c r="G74" s="80" t="n">
         <f aca="false">C74-D74</f>
         <v>14855519.562034</v>
       </c>
-      <c r="H74" s="76" t="n">
+      <c r="H74" s="94" t="n">
         <f aca="false">YEAR(B74)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="76" t="n">
+      <c r="A75" s="94" t="n">
         <v>60</v>
       </c>
       <c r="B75" s="95" t="n">
         <f aca="false">EOMONTH($C$10,59)</f>
         <v>48213</v>
       </c>
-      <c r="C75" s="81" t="n">
+      <c r="C75" s="80" t="n">
         <f aca="false">G74</f>
         <v>14855519.562034</v>
       </c>
-      <c r="D75" s="81" t="n">
+      <c r="D75" s="80" t="n">
         <f aca="false">IF(A75&gt;$C$6,MIN(C75,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E75" s="81" t="n">
+      <c r="E75" s="80" t="n">
         <f aca="false">C75*$C$8*DAY(B75)/$C$11</f>
         <v>89545.7706933719</v>
       </c>
-      <c r="F75" s="81" t="n">
+      <c r="F75" s="80" t="n">
         <f aca="false">D75+E75</f>
         <v>683766.553174734</v>
       </c>
-      <c r="G75" s="81" t="n">
+      <c r="G75" s="80" t="n">
         <f aca="false">C75-D75</f>
         <v>14261298.7795527</v>
       </c>
-      <c r="H75" s="76" t="n">
+      <c r="H75" s="94" t="n">
         <f aca="false">YEAR(B75)-YEAR($C$10)+1</f>
         <v>5</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="76" t="n">
+      <c r="A76" s="94" t="n">
         <v>61</v>
       </c>
       <c r="B76" s="95" t="n">
         <f aca="false">EOMONTH($C$10,60)</f>
         <v>48244</v>
       </c>
-      <c r="C76" s="81" t="n">
+      <c r="C76" s="80" t="n">
         <f aca="false">G75</f>
         <v>14261298.7795527</v>
       </c>
-      <c r="D76" s="81" t="n">
+      <c r="D76" s="80" t="n">
         <f aca="false">IF(A76&gt;$C$6,MIN(C76,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E76" s="81" t="n">
+      <c r="E76" s="80" t="n">
         <f aca="false">C76*$C$8*DAY(B76)/$C$11</f>
         <v>85963.939865637</v>
       </c>
-      <c r="F76" s="81" t="n">
+      <c r="F76" s="80" t="n">
         <f aca="false">D76+E76</f>
         <v>680184.722346999</v>
       </c>
-      <c r="G76" s="81" t="n">
+      <c r="G76" s="80" t="n">
         <f aca="false">C76-D76</f>
         <v>13667077.9970713</v>
       </c>
-      <c r="H76" s="76" t="n">
+      <c r="H76" s="94" t="n">
         <f aca="false">YEAR(B76)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="76" t="n">
+      <c r="A77" s="94" t="n">
         <v>62</v>
       </c>
       <c r="B77" s="95" t="n">
         <f aca="false">EOMONTH($C$10,61)</f>
         <v>48273</v>
       </c>
-      <c r="C77" s="81" t="n">
+      <c r="C77" s="80" t="n">
         <f aca="false">G76</f>
         <v>13667077.9970713</v>
       </c>
-      <c r="D77" s="81" t="n">
+      <c r="D77" s="80" t="n">
         <f aca="false">IF(A77&gt;$C$6,MIN(C77,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E77" s="81" t="n">
+      <c r="E77" s="80" t="n">
         <f aca="false">C77*$C$8*DAY(B77)/$C$11</f>
         <v>77067.1342612633</v>
       </c>
-      <c r="F77" s="81" t="n">
+      <c r="F77" s="80" t="n">
         <f aca="false">D77+E77</f>
         <v>671287.916742626</v>
       </c>
-      <c r="G77" s="81" t="n">
+      <c r="G77" s="80" t="n">
         <f aca="false">C77-D77</f>
         <v>13072857.21459</v>
       </c>
-      <c r="H77" s="76" t="n">
+      <c r="H77" s="94" t="n">
         <f aca="false">YEAR(B77)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="76" t="n">
+      <c r="A78" s="94" t="n">
         <v>63</v>
       </c>
       <c r="B78" s="95" t="n">
         <f aca="false">EOMONTH($C$10,62)</f>
         <v>48304</v>
       </c>
-      <c r="C78" s="81" t="n">
+      <c r="C78" s="80" t="n">
         <f aca="false">G77</f>
         <v>13072857.21459</v>
       </c>
-      <c r="D78" s="81" t="n">
+      <c r="D78" s="80" t="n">
         <f aca="false">IF(A78&gt;$C$6,MIN(C78,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E78" s="81" t="n">
+      <c r="E78" s="80" t="n">
         <f aca="false">C78*$C$8*DAY(B78)/$C$11</f>
         <v>78800.2782101672</v>
       </c>
-      <c r="F78" s="81" t="n">
+      <c r="F78" s="80" t="n">
         <f aca="false">D78+E78</f>
         <v>673021.060691529</v>
       </c>
-      <c r="G78" s="81" t="n">
+      <c r="G78" s="80" t="n">
         <f aca="false">C78-D78</f>
         <v>12478636.4321086</v>
       </c>
-      <c r="H78" s="76" t="n">
+      <c r="H78" s="94" t="n">
         <f aca="false">YEAR(B78)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="76" t="n">
+      <c r="A79" s="94" t="n">
         <v>64</v>
       </c>
       <c r="B79" s="95" t="n">
         <f aca="false">EOMONTH($C$10,63)</f>
         <v>48334</v>
       </c>
-      <c r="C79" s="81" t="n">
+      <c r="C79" s="80" t="n">
         <f aca="false">G78</f>
         <v>12478636.4321086</v>
       </c>
-      <c r="D79" s="81" t="n">
+      <c r="D79" s="80" t="n">
         <f aca="false">IF(A79&gt;$C$6,MIN(C79,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E79" s="81" t="n">
+      <c r="E79" s="80" t="n">
         <f aca="false">C79*$C$8*DAY(B79)/$C$11</f>
         <v>72792.0458539668</v>
       </c>
-      <c r="F79" s="81" t="n">
+      <c r="F79" s="80" t="n">
         <f aca="false">D79+E79</f>
         <v>667012.828335329</v>
       </c>
-      <c r="G79" s="81" t="n">
+      <c r="G79" s="80" t="n">
         <f aca="false">C79-D79</f>
         <v>11884415.6496272</v>
       </c>
-      <c r="H79" s="76" t="n">
+      <c r="H79" s="94" t="n">
         <f aca="false">YEAR(B79)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="76" t="n">
+      <c r="A80" s="94" t="n">
         <v>65</v>
       </c>
       <c r="B80" s="95" t="n">
         <f aca="false">EOMONTH($C$10,64)</f>
         <v>48365</v>
       </c>
-      <c r="C80" s="81" t="n">
+      <c r="C80" s="80" t="n">
         <f aca="false">G79</f>
         <v>11884415.6496272</v>
       </c>
-      <c r="D80" s="81" t="n">
+      <c r="D80" s="80" t="n">
         <f aca="false">IF(A80&gt;$C$6,MIN(C80,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E80" s="81" t="n">
+      <c r="E80" s="80" t="n">
         <f aca="false">C80*$C$8*DAY(B80)/$C$11</f>
         <v>71636.6165546975</v>
       </c>
-      <c r="F80" s="81" t="n">
+      <c r="F80" s="80" t="n">
         <f aca="false">D80+E80</f>
         <v>665857.39903606</v>
       </c>
-      <c r="G80" s="81" t="n">
+      <c r="G80" s="80" t="n">
         <f aca="false">C80-D80</f>
         <v>11290194.8671459</v>
       </c>
-      <c r="H80" s="76" t="n">
+      <c r="H80" s="94" t="n">
         <f aca="false">YEAR(B80)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="76" t="n">
+      <c r="A81" s="94" t="n">
         <v>66</v>
       </c>
       <c r="B81" s="95" t="n">
         <f aca="false">EOMONTH($C$10,65)</f>
         <v>48395</v>
       </c>
-      <c r="C81" s="81" t="n">
+      <c r="C81" s="80" t="n">
         <f aca="false">G80</f>
         <v>11290194.8671459</v>
       </c>
-      <c r="D81" s="81" t="n">
+      <c r="D81" s="80" t="n">
         <f aca="false">IF(A81&gt;$C$6,MIN(C81,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E81" s="81" t="n">
+      <c r="E81" s="80" t="n">
         <f aca="false">C81*$C$8*DAY(B81)/$C$11</f>
         <v>65859.4700583509</v>
       </c>
-      <c r="F81" s="81" t="n">
+      <c r="F81" s="80" t="n">
         <f aca="false">D81+E81</f>
         <v>660080.252539713</v>
       </c>
-      <c r="G81" s="81" t="n">
+      <c r="G81" s="80" t="n">
         <f aca="false">C81-D81</f>
         <v>10695974.0846645</v>
       </c>
-      <c r="H81" s="76" t="n">
+      <c r="H81" s="94" t="n">
         <f aca="false">YEAR(B81)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="76" t="n">
+      <c r="A82" s="94" t="n">
         <v>67</v>
       </c>
       <c r="B82" s="95" t="n">
         <f aca="false">EOMONTH($C$10,66)</f>
         <v>48426</v>
       </c>
-      <c r="C82" s="81" t="n">
+      <c r="C82" s="80" t="n">
         <f aca="false">G81</f>
         <v>10695974.0846645</v>
       </c>
-      <c r="D82" s="81" t="n">
+      <c r="D82" s="80" t="n">
         <f aca="false">IF(A82&gt;$C$6,MIN(C82,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E82" s="81" t="n">
+      <c r="E82" s="80" t="n">
         <f aca="false">C82*$C$8*DAY(B82)/$C$11</f>
         <v>64472.9548992277</v>
       </c>
-      <c r="F82" s="81" t="n">
+      <c r="F82" s="80" t="n">
         <f aca="false">D82+E82</f>
         <v>658693.73738059</v>
       </c>
-      <c r="G82" s="81" t="n">
+      <c r="G82" s="80" t="n">
         <f aca="false">C82-D82</f>
         <v>10101753.3021831</v>
       </c>
-      <c r="H82" s="76" t="n">
+      <c r="H82" s="94" t="n">
         <f aca="false">YEAR(B82)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="76" t="n">
+      <c r="A83" s="94" t="n">
         <v>68</v>
       </c>
       <c r="B83" s="95" t="n">
         <f aca="false">EOMONTH($C$10,67)</f>
         <v>48457</v>
       </c>
-      <c r="C83" s="81" t="n">
+      <c r="C83" s="80" t="n">
         <f aca="false">G82</f>
         <v>10101753.3021831</v>
       </c>
-      <c r="D83" s="81" t="n">
+      <c r="D83" s="80" t="n">
         <f aca="false">IF(A83&gt;$C$6,MIN(C83,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E83" s="81" t="n">
+      <c r="E83" s="80" t="n">
         <f aca="false">C83*$C$8*DAY(B83)/$C$11</f>
         <v>60891.1240714928</v>
       </c>
-      <c r="F83" s="81" t="n">
+      <c r="F83" s="80" t="n">
         <f aca="false">D83+E83</f>
         <v>655111.906552855</v>
       </c>
-      <c r="G83" s="81" t="n">
+      <c r="G83" s="80" t="n">
         <f aca="false">C83-D83</f>
         <v>9507532.51970177</v>
       </c>
-      <c r="H83" s="76" t="n">
+      <c r="H83" s="94" t="n">
         <f aca="false">YEAR(B83)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="76" t="n">
+      <c r="A84" s="94" t="n">
         <v>69</v>
       </c>
       <c r="B84" s="95" t="n">
         <f aca="false">EOMONTH($C$10,68)</f>
         <v>48487</v>
       </c>
-      <c r="C84" s="81" t="n">
+      <c r="C84" s="80" t="n">
         <f aca="false">G83</f>
         <v>9507532.51970177</v>
       </c>
-      <c r="D84" s="81" t="n">
+      <c r="D84" s="80" t="n">
         <f aca="false">IF(A84&gt;$C$6,MIN(C84,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E84" s="81" t="n">
+      <c r="E84" s="80" t="n">
         <f aca="false">C84*$C$8*DAY(B84)/$C$11</f>
         <v>55460.606364927</v>
       </c>
-      <c r="F84" s="81" t="n">
+      <c r="F84" s="80" t="n">
         <f aca="false">D84+E84</f>
         <v>649681.388846289</v>
       </c>
-      <c r="G84" s="81" t="n">
+      <c r="G84" s="80" t="n">
         <f aca="false">C84-D84</f>
         <v>8913311.73722041</v>
       </c>
-      <c r="H84" s="76" t="n">
+      <c r="H84" s="94" t="n">
         <f aca="false">YEAR(B84)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="76" t="n">
+      <c r="A85" s="94" t="n">
         <v>70</v>
       </c>
       <c r="B85" s="95" t="n">
         <f aca="false">EOMONTH($C$10,69)</f>
         <v>48518</v>
       </c>
-      <c r="C85" s="81" t="n">
+      <c r="C85" s="80" t="n">
         <f aca="false">G84</f>
         <v>8913311.73722041</v>
       </c>
-      <c r="D85" s="81" t="n">
+      <c r="D85" s="80" t="n">
         <f aca="false">IF(A85&gt;$C$6,MIN(C85,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E85" s="81" t="n">
+      <c r="E85" s="80" t="n">
         <f aca="false">C85*$C$8*DAY(B85)/$C$11</f>
         <v>53727.462416023</v>
       </c>
-      <c r="F85" s="81" t="n">
+      <c r="F85" s="80" t="n">
         <f aca="false">D85+E85</f>
         <v>647948.244897385</v>
       </c>
-      <c r="G85" s="81" t="n">
+      <c r="G85" s="80" t="n">
         <f aca="false">C85-D85</f>
         <v>8319090.95473905</v>
       </c>
-      <c r="H85" s="76" t="n">
+      <c r="H85" s="94" t="n">
         <f aca="false">YEAR(B85)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="76" t="n">
+      <c r="A86" s="94" t="n">
         <v>71</v>
       </c>
       <c r="B86" s="95" t="n">
         <f aca="false">EOMONTH($C$10,70)</f>
         <v>48548</v>
       </c>
-      <c r="C86" s="81" t="n">
+      <c r="C86" s="80" t="n">
         <f aca="false">G85</f>
         <v>8319090.95473905</v>
       </c>
-      <c r="D86" s="81" t="n">
+      <c r="D86" s="80" t="n">
         <f aca="false">IF(A86&gt;$C$6,MIN(C86,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E86" s="81" t="n">
+      <c r="E86" s="80" t="n">
         <f aca="false">C86*$C$8*DAY(B86)/$C$11</f>
         <v>48528.0305693111</v>
       </c>
-      <c r="F86" s="81" t="n">
+      <c r="F86" s="80" t="n">
         <f aca="false">D86+E86</f>
         <v>642748.813050673</v>
       </c>
-      <c r="G86" s="81" t="n">
+      <c r="G86" s="80" t="n">
         <f aca="false">C86-D86</f>
         <v>7724870.17225769</v>
       </c>
-      <c r="H86" s="76" t="n">
+      <c r="H86" s="94" t="n">
         <f aca="false">YEAR(B86)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="76" t="n">
+      <c r="A87" s="94" t="n">
         <v>72</v>
       </c>
       <c r="B87" s="95" t="n">
         <f aca="false">EOMONTH($C$10,71)</f>
         <v>48579</v>
       </c>
-      <c r="C87" s="81" t="n">
+      <c r="C87" s="80" t="n">
         <f aca="false">G86</f>
         <v>7724870.17225769</v>
       </c>
-      <c r="D87" s="81" t="n">
+      <c r="D87" s="80" t="n">
         <f aca="false">IF(A87&gt;$C$6,MIN(C87,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E87" s="81" t="n">
+      <c r="E87" s="80" t="n">
         <f aca="false">C87*$C$8*DAY(B87)/$C$11</f>
         <v>46563.8007605533</v>
       </c>
-      <c r="F87" s="81" t="n">
+      <c r="F87" s="80" t="n">
         <f aca="false">D87+E87</f>
         <v>640784.583241916</v>
       </c>
-      <c r="G87" s="81" t="n">
+      <c r="G87" s="80" t="n">
         <f aca="false">C87-D87</f>
         <v>7130649.38977632</v>
       </c>
-      <c r="H87" s="76" t="n">
+      <c r="H87" s="94" t="n">
         <f aca="false">YEAR(B87)-YEAR($C$10)+1</f>
         <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="76" t="n">
+      <c r="A88" s="94" t="n">
         <v>73</v>
       </c>
       <c r="B88" s="95" t="n">
         <f aca="false">EOMONTH($C$10,72)</f>
         <v>48610</v>
       </c>
-      <c r="C88" s="81" t="n">
+      <c r="C88" s="80" t="n">
         <f aca="false">G87</f>
         <v>7130649.38977632</v>
       </c>
-      <c r="D88" s="81" t="n">
+      <c r="D88" s="80" t="n">
         <f aca="false">IF(A88&gt;$C$6,MIN(C88,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E88" s="81" t="n">
+      <c r="E88" s="80" t="n">
         <f aca="false">C88*$C$8*DAY(B88)/$C$11</f>
         <v>42981.9699328184</v>
       </c>
-      <c r="F88" s="81" t="n">
+      <c r="F88" s="80" t="n">
         <f aca="false">D88+E88</f>
         <v>637202.752414181</v>
       </c>
-      <c r="G88" s="81" t="n">
+      <c r="G88" s="80" t="n">
         <f aca="false">C88-D88</f>
         <v>6536428.60729496</v>
       </c>
-      <c r="H88" s="76" t="n">
+      <c r="H88" s="94" t="n">
         <f aca="false">YEAR(B88)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="76" t="n">
+      <c r="A89" s="94" t="n">
         <v>74</v>
       </c>
       <c r="B89" s="95" t="n">
         <f aca="false">EOMONTH($C$10,73)</f>
         <v>48638</v>
       </c>
-      <c r="C89" s="81" t="n">
+      <c r="C89" s="80" t="n">
         <f aca="false">G88</f>
         <v>6536428.60729496</v>
       </c>
-      <c r="D89" s="81" t="n">
+      <c r="D89" s="80" t="n">
         <f aca="false">IF(A89&gt;$C$6,MIN(C89,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E89" s="81" t="n">
+      <c r="E89" s="80" t="n">
         <f aca="false">C89*$C$8*DAY(B89)/$C$11</f>
         <v>35587.2224174948</v>
       </c>
-      <c r="F89" s="81" t="n">
+      <c r="F89" s="80" t="n">
         <f aca="false">D89+E89</f>
         <v>629808.004898857</v>
       </c>
-      <c r="G89" s="81" t="n">
+      <c r="G89" s="80" t="n">
         <f aca="false">C89-D89</f>
         <v>5942207.8248136</v>
       </c>
-      <c r="H89" s="76" t="n">
+      <c r="H89" s="94" t="n">
         <f aca="false">YEAR(B89)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="76" t="n">
+      <c r="A90" s="94" t="n">
         <v>75</v>
       </c>
       <c r="B90" s="95" t="n">
         <f aca="false">EOMONTH($C$10,74)</f>
         <v>48669</v>
       </c>
-      <c r="C90" s="81" t="n">
+      <c r="C90" s="80" t="n">
         <f aca="false">G89</f>
         <v>5942207.8248136</v>
       </c>
-      <c r="D90" s="81" t="n">
+      <c r="D90" s="80" t="n">
         <f aca="false">IF(A90&gt;$C$6,MIN(C90,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E90" s="81" t="n">
+      <c r="E90" s="80" t="n">
         <f aca="false">C90*$C$8*DAY(B90)/$C$11</f>
         <v>35818.3082773486</v>
       </c>
-      <c r="F90" s="81" t="n">
+      <c r="F90" s="80" t="n">
         <f aca="false">D90+E90</f>
         <v>630039.090758711</v>
       </c>
-      <c r="G90" s="81" t="n">
+      <c r="G90" s="80" t="n">
         <f aca="false">C90-D90</f>
         <v>5347987.04233224</v>
       </c>
-      <c r="H90" s="76" t="n">
+      <c r="H90" s="94" t="n">
         <f aca="false">YEAR(B90)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="76" t="n">
+      <c r="A91" s="94" t="n">
         <v>76</v>
       </c>
       <c r="B91" s="95" t="n">
         <f aca="false">EOMONTH($C$10,75)</f>
         <v>48699</v>
       </c>
-      <c r="C91" s="81" t="n">
+      <c r="C91" s="80" t="n">
         <f aca="false">G90</f>
         <v>5347987.04233224</v>
       </c>
-      <c r="D91" s="81" t="n">
+      <c r="D91" s="80" t="n">
         <f aca="false">IF(A91&gt;$C$6,MIN(C91,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E91" s="81" t="n">
+      <c r="E91" s="80" t="n">
         <f aca="false">C91*$C$8*DAY(B91)/$C$11</f>
         <v>31196.5910802714</v>
       </c>
-      <c r="F91" s="81" t="n">
+      <c r="F91" s="80" t="n">
         <f aca="false">D91+E91</f>
         <v>625417.373561634</v>
       </c>
-      <c r="G91" s="81" t="n">
+      <c r="G91" s="80" t="n">
         <f aca="false">C91-D91</f>
         <v>4753766.25985088</v>
       </c>
-      <c r="H91" s="76" t="n">
+      <c r="H91" s="94" t="n">
         <f aca="false">YEAR(B91)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="76" t="n">
+      <c r="A92" s="94" t="n">
         <v>77</v>
       </c>
       <c r="B92" s="95" t="n">
         <f aca="false">EOMONTH($C$10,76)</f>
         <v>48730</v>
       </c>
-      <c r="C92" s="81" t="n">
+      <c r="C92" s="80" t="n">
         <f aca="false">G91</f>
         <v>4753766.25985088</v>
       </c>
-      <c r="D92" s="81" t="n">
+      <c r="D92" s="80" t="n">
         <f aca="false">IF(A92&gt;$C$6,MIN(C92,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E92" s="81" t="n">
+      <c r="E92" s="80" t="n">
         <f aca="false">C92*$C$8*DAY(B92)/$C$11</f>
         <v>28654.6466218789</v>
       </c>
-      <c r="F92" s="81" t="n">
+      <c r="F92" s="80" t="n">
         <f aca="false">D92+E92</f>
         <v>622875.429103241</v>
       </c>
-      <c r="G92" s="81" t="n">
+      <c r="G92" s="80" t="n">
         <f aca="false">C92-D92</f>
         <v>4159545.47736951</v>
       </c>
-      <c r="H92" s="76" t="n">
+      <c r="H92" s="94" t="n">
         <f aca="false">YEAR(B92)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="76" t="n">
+      <c r="A93" s="94" t="n">
         <v>78</v>
       </c>
       <c r="B93" s="95" t="n">
         <f aca="false">EOMONTH($C$10,77)</f>
         <v>48760</v>
       </c>
-      <c r="C93" s="81" t="n">
+      <c r="C93" s="80" t="n">
         <f aca="false">G92</f>
         <v>4159545.47736951</v>
       </c>
-      <c r="D93" s="81" t="n">
+      <c r="D93" s="80" t="n">
         <f aca="false">IF(A93&gt;$C$6,MIN(C93,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E93" s="81" t="n">
+      <c r="E93" s="80" t="n">
         <f aca="false">C93*$C$8*DAY(B93)/$C$11</f>
         <v>24264.0152846555</v>
       </c>
-      <c r="F93" s="81" t="n">
+      <c r="F93" s="80" t="n">
         <f aca="false">D93+E93</f>
         <v>618484.797766018</v>
       </c>
-      <c r="G93" s="81" t="n">
+      <c r="G93" s="80" t="n">
         <f aca="false">C93-D93</f>
         <v>3565324.69488815</v>
       </c>
-      <c r="H93" s="76" t="n">
+      <c r="H93" s="94" t="n">
         <f aca="false">YEAR(B93)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="76" t="n">
+      <c r="A94" s="94" t="n">
         <v>79</v>
       </c>
       <c r="B94" s="95" t="n">
         <f aca="false">EOMONTH($C$10,78)</f>
         <v>48791</v>
       </c>
-      <c r="C94" s="81" t="n">
+      <c r="C94" s="80" t="n">
         <f aca="false">G93</f>
         <v>3565324.69488815</v>
       </c>
-      <c r="D94" s="81" t="n">
+      <c r="D94" s="80" t="n">
         <f aca="false">IF(A94&gt;$C$6,MIN(C94,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E94" s="81" t="n">
+      <c r="E94" s="80" t="n">
         <f aca="false">C94*$C$8*DAY(B94)/$C$11</f>
         <v>21490.9849664091</v>
       </c>
-      <c r="F94" s="81" t="n">
+      <c r="F94" s="80" t="n">
         <f aca="false">D94+E94</f>
         <v>615711.767447771</v>
       </c>
-      <c r="G94" s="81" t="n">
+      <c r="G94" s="80" t="n">
         <f aca="false">C94-D94</f>
         <v>2971103.91240679</v>
       </c>
-      <c r="H94" s="76" t="n">
+      <c r="H94" s="94" t="n">
         <f aca="false">YEAR(B94)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="76" t="n">
+      <c r="A95" s="94" t="n">
         <v>80</v>
       </c>
       <c r="B95" s="95" t="n">
         <f aca="false">EOMONTH($C$10,79)</f>
         <v>48822</v>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C95" s="80" t="n">
         <f aca="false">G94</f>
         <v>2971103.91240679</v>
       </c>
-      <c r="D95" s="81" t="n">
+      <c r="D95" s="80" t="n">
         <f aca="false">IF(A95&gt;$C$6,MIN(C95,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E95" s="81" t="n">
+      <c r="E95" s="80" t="n">
         <f aca="false">C95*$C$8*DAY(B95)/$C$11</f>
         <v>17909.1541386743</v>
       </c>
-      <c r="F95" s="81" t="n">
+      <c r="F95" s="80" t="n">
         <f aca="false">D95+E95</f>
         <v>612129.936620037</v>
       </c>
-      <c r="G95" s="81" t="n">
+      <c r="G95" s="80" t="n">
         <f aca="false">C95-D95</f>
         <v>2376883.12992543</v>
       </c>
-      <c r="H95" s="76" t="n">
+      <c r="H95" s="94" t="n">
         <f aca="false">YEAR(B95)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="76" t="n">
+      <c r="A96" s="94" t="n">
         <v>81</v>
       </c>
       <c r="B96" s="95" t="n">
         <f aca="false">EOMONTH($C$10,80)</f>
         <v>48852</v>
       </c>
-      <c r="C96" s="81" t="n">
+      <c r="C96" s="80" t="n">
         <f aca="false">G95</f>
         <v>2376883.12992543</v>
       </c>
-      <c r="D96" s="81" t="n">
+      <c r="D96" s="80" t="n">
         <f aca="false">IF(A96&gt;$C$6,MIN(C96,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E96" s="81" t="n">
+      <c r="E96" s="80" t="n">
         <f aca="false">C96*$C$8*DAY(B96)/$C$11</f>
         <v>13865.1515912317</v>
       </c>
-      <c r="F96" s="81" t="n">
+      <c r="F96" s="80" t="n">
         <f aca="false">D96+E96</f>
         <v>608085.934072594</v>
       </c>
-      <c r="G96" s="81" t="n">
+      <c r="G96" s="80" t="n">
         <f aca="false">C96-D96</f>
         <v>1782662.34744407</v>
       </c>
-      <c r="H96" s="76" t="n">
+      <c r="H96" s="94" t="n">
         <f aca="false">YEAR(B96)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="76" t="n">
+      <c r="A97" s="94" t="n">
         <v>82</v>
       </c>
       <c r="B97" s="95" t="n">
         <f aca="false">EOMONTH($C$10,81)</f>
         <v>48883</v>
       </c>
-      <c r="C97" s="81" t="n">
+      <c r="C97" s="80" t="n">
         <f aca="false">G96</f>
         <v>1782662.34744407</v>
       </c>
-      <c r="D97" s="81" t="n">
+      <c r="D97" s="80" t="n">
         <f aca="false">IF(A97&gt;$C$6,MIN(C97,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E97" s="81" t="n">
+      <c r="E97" s="80" t="n">
         <f aca="false">C97*$C$8*DAY(B97)/$C$11</f>
         <v>10745.4924832045</v>
       </c>
-      <c r="F97" s="81" t="n">
+      <c r="F97" s="80" t="n">
         <f aca="false">D97+E97</f>
         <v>604966.274964567</v>
       </c>
-      <c r="G97" s="81" t="n">
+      <c r="G97" s="80" t="n">
         <f aca="false">C97-D97</f>
         <v>1188441.5649627</v>
       </c>
-      <c r="H97" s="76" t="n">
+      <c r="H97" s="94" t="n">
         <f aca="false">YEAR(B97)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="76" t="n">
+      <c r="A98" s="94" t="n">
         <v>83</v>
       </c>
       <c r="B98" s="95" t="n">
         <f aca="false">EOMONTH($C$10,82)</f>
         <v>48913</v>
       </c>
-      <c r="C98" s="81" t="n">
+      <c r="C98" s="80" t="n">
         <f aca="false">G97</f>
         <v>1188441.5649627</v>
       </c>
-      <c r="D98" s="81" t="n">
+      <c r="D98" s="80" t="n">
         <f aca="false">IF(A98&gt;$C$6,MIN(C98,$C$13),0)</f>
         <v>594220.782481362</v>
       </c>
-      <c r="E98" s="81" t="n">
+      <c r="E98" s="80" t="n">
         <f aca="false">C98*$C$8*DAY(B98)/$C$11</f>
         <v>6932.57579561577</v>
       </c>
-      <c r="F98" s="81" t="n">
+      <c r="F98" s="80" t="n">
         <f aca="false">D98+E98</f>
         <v>601153.358276978</v>
       </c>
-      <c r="G98" s="81" t="n">
+      <c r="G98" s="80" t="n">
         <f aca="false">C98-D98</f>
         <v>594220.782481341</v>
       </c>
-      <c r="H98" s="76" t="n">
+      <c r="H98" s="94" t="n">
         <f aca="false">YEAR(B98)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="76" t="n">
+      <c r="A99" s="94" t="n">
         <v>84</v>
       </c>
       <c r="B99" s="95" t="n">
         <f aca="false">EOMONTH($C$10,83)</f>
         <v>48944</v>
       </c>
-      <c r="C99" s="81" t="n">
+      <c r="C99" s="80" t="n">
         <f aca="false">G98</f>
         <v>594220.782481341</v>
       </c>
-      <c r="D99" s="81" t="n">
+      <c r="D99" s="80" t="n">
         <f aca="false">IF(A99&gt;$C$6,MIN(C99,$C$13),0)</f>
         <v>594220.782481341</v>
       </c>
-      <c r="E99" s="81" t="n">
+      <c r="E99" s="80" t="n">
         <f aca="false">C99*$C$8*DAY(B99)/$C$11</f>
         <v>3581.83082773475</v>
       </c>
-      <c r="F99" s="81" t="n">
+      <c r="F99" s="80" t="n">
         <f aca="false">D99+E99</f>
         <v>597802.613309075</v>
       </c>
-      <c r="G99" s="81" t="n">
+      <c r="G99" s="80" t="n">
         <f aca="false">C99-D99</f>
         <v>0</v>
       </c>
-      <c r="H99" s="76" t="n">
+      <c r="H99" s="94" t="n">
         <f aca="false">YEAR(B99)-YEAR($C$10)+1</f>
         <v>7</v>
       </c>
@@ -9580,7 +9575,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="37" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9611,7 +9606,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C104" s="13" t="n">
         <f aca="false">$C$9</f>
@@ -9671,7 +9666,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C106" s="13" t="n">
         <f aca="false">SUMIF($H$16:$H$99,1,$E$16:$E$99)</f>
@@ -9704,7 +9699,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C107" s="13" t="n">
         <f aca="false">C105+C106</f>
@@ -9737,7 +9732,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="25" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C108" s="13" t="n">
         <f aca="false">$C$9-SUM($C$105:C105)</f>
@@ -9795,10 +9790,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9843,7 +9838,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -9879,7 +9874,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -9915,7 +9910,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -9951,7 +9946,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -9986,10 +9981,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="C10" s="78" t="s">
+      <c r="B10" s="90" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="61" t="n">
@@ -10023,79 +10018,79 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">CostSold!D19</f>
-        <v>11316650.7201236</v>
+        <v>11266042.9168156</v>
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">CostSold!E19</f>
-        <v>43392941.6724242</v>
+        <v>43241118.2625002</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">CostSold!F19</f>
-        <v>49091211.8766119</v>
+        <v>48939388.4666879</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">CostSold!G19</f>
-        <v>58338443.9283732</v>
+        <v>58186620.5184492</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">CostSold!H19</f>
-        <v>59738918.0634507</v>
+        <v>59587094.6535267</v>
       </c>
       <c r="I11" s="13" t="n">
         <f aca="false">CostSold!I19</f>
-        <v>60820556.2151245</v>
+        <v>60668732.8052005</v>
       </c>
       <c r="J11" s="13" t="n">
         <f aca="false">CostSold!J19</f>
-        <v>61934685.8487086</v>
+        <v>61782862.4387846</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">CostSold!D21</f>
-        <v>11316650.7201236</v>
+        <v>11266042.9168156</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">CostSold!E21</f>
-        <v>43392941.6724242</v>
+        <v>43241118.2625002</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">CostSold!F21</f>
-        <v>49091211.8766119</v>
+        <v>48939388.4666879</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">CostSold!G21</f>
-        <v>58338443.9283732</v>
+        <v>58186620.5184492</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">CostSold!H21</f>
-        <v>59738918.0634507</v>
+        <v>59587094.6535267</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">CostSold!I21</f>
-        <v>60820556.2151245</v>
+        <v>60668732.8052005</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">CostSold!J21</f>
-        <v>61934685.8487086</v>
+        <v>61782862.4387846</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>34</v>
@@ -10130,44 +10125,44 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="91" t="s">
-        <v>437</v>
-      </c>
-      <c r="C14" s="78" t="s">
+      <c r="B14" s="90" t="s">
+        <v>435</v>
+      </c>
+      <c r="C14" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="61" t="n">
         <f aca="false">D10-D11</f>
-        <v>12544934.2122294</v>
+        <v>12595542.0155374</v>
       </c>
       <c r="E14" s="61" t="n">
         <f aca="false">E10-E11</f>
-        <v>41690626.7282677</v>
+        <v>41842450.1381917</v>
       </c>
       <c r="F14" s="61" t="n">
         <f aca="false">F10-F11</f>
-        <v>44945759.3582497</v>
+        <v>45097582.7681736</v>
       </c>
       <c r="G14" s="61" t="n">
         <f aca="false">G10-G11</f>
-        <v>63757687.3538119</v>
+        <v>63909510.7637359</v>
       </c>
       <c r="H14" s="61" t="n">
         <f aca="false">H10-H11</f>
-        <v>60224084.1600402</v>
+        <v>60375907.5699642</v>
       </c>
       <c r="I14" s="61" t="n">
         <f aca="false">I10-I11</f>
-        <v>61700034.7926609</v>
+        <v>61851858.2025848</v>
       </c>
       <c r="J14" s="61" t="n">
         <f aca="false">J10-J11</f>
-        <v>63281844.4151321</v>
+        <v>63433667.8250562</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>34</v>
@@ -10203,7 +10198,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>34</v>
@@ -10238,51 +10233,51 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="91" t="s">
-        <v>440</v>
-      </c>
-      <c r="C17" s="78" t="s">
+      <c r="B17" s="90" t="s">
+        <v>438</v>
+      </c>
+      <c r="C17" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="61" t="n">
         <f aca="false">D14-D15-D16</f>
-        <v>5747408.76177281</v>
+        <v>5798016.5650808</v>
       </c>
       <c r="E17" s="61" t="n">
         <f aca="false">E14-E15-E16</f>
-        <v>37007527.6179095</v>
+        <v>37159351.0278334</v>
       </c>
       <c r="F17" s="61" t="n">
         <f aca="false">F14-F15-F16</f>
-        <v>39866172.2931889</v>
+        <v>40017995.7031128</v>
       </c>
       <c r="G17" s="61" t="n">
         <f aca="false">G14-G15-G16</f>
-        <v>46714726.0221253</v>
+        <v>46866549.4320493</v>
       </c>
       <c r="H17" s="61" t="n">
         <f aca="false">H14-H15-H16</f>
-        <v>35593973.3808443</v>
+        <v>35745796.7907683</v>
       </c>
       <c r="I17" s="61" t="n">
         <f aca="false">I14-I15-I16</f>
-        <v>36482031.5524271</v>
+        <v>36633854.962351</v>
       </c>
       <c r="J17" s="61" t="n">
         <f aca="false">J14-J15-J16</f>
-        <v>37431000.0875241</v>
+        <v>37582823.4974481</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">D19</f>
-        <v>0</v>
+        <v>3036468.19847976</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">E19</f>
@@ -10311,14 +10306,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="13" t="n">
         <f aca="false">CostSold!D40</f>
-        <v>0</v>
+        <v>3036468.19847976</v>
       </c>
       <c r="E19" s="13" t="n">
         <f aca="false">CostSold!E40</f>
@@ -10346,188 +10341,188 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="91" t="s">
-        <v>443</v>
-      </c>
-      <c r="C20" s="78" t="s">
+      <c r="B20" s="90" t="s">
+        <v>441</v>
+      </c>
+      <c r="C20" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="61" t="n">
         <f aca="false">D17-D18</f>
-        <v>5747408.76177281</v>
+        <v>2761548.36660104</v>
       </c>
       <c r="E20" s="61" t="n">
         <f aca="false">E17-E18</f>
-        <v>34195905.9610675</v>
+        <v>34347729.3709915</v>
       </c>
       <c r="F20" s="61" t="n">
         <f aca="false">F17-F18</f>
-        <v>37568832.2174517</v>
+        <v>37720655.6273757</v>
       </c>
       <c r="G20" s="61" t="n">
         <f aca="false">G17-G18</f>
-        <v>44923463.9794681</v>
+        <v>45075287.3893921</v>
       </c>
       <c r="H20" s="61" t="n">
         <f aca="false">H17-H18</f>
-        <v>34308789.371267</v>
+        <v>34460612.781191</v>
       </c>
       <c r="I20" s="61" t="n">
         <f aca="false">I17-I18</f>
-        <v>35700268.0885415</v>
+        <v>35852091.4984654</v>
       </c>
       <c r="J20" s="61" t="n">
         <f aca="false">J17-J18</f>
-        <v>37157972.1441068</v>
+        <v>37309795.5540308</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="13" t="n">
         <f aca="false">Taxes!D29</f>
-        <v>2205838.25258854</v>
+        <v>1981898.72295066</v>
       </c>
       <c r="E21" s="13" t="n">
         <f aca="false">Taxes!E29</f>
-        <v>14757263.3710805</v>
+        <v>14780036.8825691</v>
       </c>
       <c r="F21" s="13" t="n">
         <f aca="false">Taxes!F29</f>
-        <v>16276350.5249837</v>
+        <v>16299124.0364723</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">Taxes!G29</f>
-        <v>20554660.7683254</v>
+        <v>20577434.279814</v>
       </c>
       <c r="H21" s="13" t="n">
         <f aca="false">Taxes!H29</f>
-        <v>18721079.1836114</v>
+        <v>18743852.6951</v>
       </c>
       <c r="I21" s="13" t="n">
         <f aca="false">Taxes!I29</f>
-        <v>19219212.3536359</v>
+        <v>19241985.8651245</v>
       </c>
       <c r="J21" s="13" t="n">
         <f aca="false">Taxes!J29</f>
-        <v>19742934.7725243</v>
+        <v>19765708.2840129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="38" t="s">
-        <v>445</v>
-      </c>
-      <c r="C22" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="C22" s="82" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="16" t="n">
         <f aca="false">D20-D21</f>
-        <v>3541570.50918427</v>
+        <v>779649.643650383</v>
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">E20-E21</f>
-        <v>19438642.589987</v>
+        <v>19567692.4884224</v>
       </c>
       <c r="F22" s="16" t="n">
         <f aca="false">F20-F21</f>
-        <v>21292481.692468</v>
+        <v>21421531.5909034</v>
       </c>
       <c r="G22" s="16" t="n">
         <f aca="false">G20-G21</f>
-        <v>24368803.2111427</v>
+        <v>24497853.1095781</v>
       </c>
       <c r="H22" s="16" t="n">
         <f aca="false">H20-H21</f>
-        <v>15587710.1876556</v>
+        <v>15716760.086091</v>
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">I20-I21</f>
-        <v>16481055.7349056</v>
+        <v>16610105.6333409</v>
       </c>
       <c r="J22" s="16" t="n">
         <f aca="false">J20-J21</f>
-        <v>17415037.3715825</v>
+        <v>17544087.2700179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="37" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">IFERROR(D14/D10,0)</f>
-        <v>0.52573767617675</v>
+        <v>0.527858566446674</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">IFERROR(E14/E10,0)</f>
-        <v>0.48999621797631</v>
+        <v>0.491780621390245</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">IFERROR(F14/F10,0)</f>
-        <v>0.477958389854939</v>
+        <v>0.47957289751007</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">IFERROR(G14/G10,0)</f>
-        <v>0.52219252718546</v>
+        <v>0.523436001555447</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">IFERROR(H14/H10,0)</f>
-        <v>0.502022148860886</v>
+        <v>0.503287734142265</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">IFERROR(I14/I10,0)</f>
-        <v>0.503589105187554</v>
+        <v>0.504828271671123</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">IFERROR(J14/J10,0)</f>
-        <v>0.505379315988013</v>
+        <v>0.506591802946437</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D26" s="14" t="n">
         <f aca="false">IFERROR(D22/D10,0)</f>
-        <v>0.148421427965684</v>
+        <v>0.0326738414845733</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">IFERROR(E22/E10,0)</f>
-        <v>0.228465295419237</v>
+        <v>0.229982038321082</v>
       </c>
       <c r="F26" s="14" t="n">
         <f aca="false">IFERROR(F22/F10,0)</f>
-        <v>0.226426706569367</v>
+        <v>0.227799038076228</v>
       </c>
       <c r="G26" s="14" t="n">
         <f aca="false">IFERROR(G22/G10,0)</f>
-        <v>0.199587021760929</v>
+        <v>0.200643974975418</v>
       </c>
       <c r="H26" s="14" t="n">
         <f aca="false">IFERROR(H22/H10,0)</f>
-        <v>0.129937646597205</v>
+        <v>0.131013394086376</v>
       </c>
       <c r="I26" s="14" t="n">
         <f aca="false">IFERROR(I22/I10,0)</f>
-        <v>0.134516619609338</v>
+        <v>0.135569911120372</v>
       </c>
       <c r="J26" s="14" t="n">
         <f aca="false">IFERROR(J22/J10,0)</f>
-        <v>0.139079379814212</v>
+        <v>0.140109993728872</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10538,40 +10533,40 @@
         <v>34</v>
       </c>
       <c r="D27" s="13" t="n">
-        <f aca="false">D17+Depreciate!$G$19</f>
+        <f aca="false">D17+Depreciate!$G$18</f>
         <v>11035331.3798956</v>
       </c>
       <c r="E27" s="13" t="n">
-        <f aca="false">E17+Depreciate!$H$19</f>
+        <f aca="false">E17+Depreciate!$H$18</f>
         <v>53030081.1865636</v>
       </c>
       <c r="F27" s="13" t="n">
-        <f aca="false">F17+Depreciate!$I$19</f>
-        <v>56029868.7189859</v>
+        <f aca="false">F17+Depreciate!$I$18</f>
+        <v>56029868.7189858</v>
       </c>
       <c r="G27" s="13" t="n">
-        <f aca="false">G17+Depreciate!$J$19</f>
+        <f aca="false">G17+Depreciate!$J$18</f>
         <v>63019565.3050652</v>
       </c>
       <c r="H27" s="13" t="n">
-        <f aca="false">H17+Depreciate!$K$19</f>
+        <f aca="false">H17+Depreciate!$K$18</f>
         <v>52039955.520927</v>
       </c>
       <c r="I27" s="13" t="n">
-        <f aca="false">I17+Depreciate!$L$19</f>
-        <v>53069156.5496527</v>
+        <f aca="false">I17+Depreciate!$L$18</f>
+        <v>53069156.5496526</v>
       </c>
       <c r="J27" s="13" t="n">
-        <f aca="false">J17+Depreciate!$M$19</f>
+        <f aca="false">J17+Depreciate!$M$18</f>
         <v>54159267.9418926</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">IFERROR(D27/D10,0)</f>
@@ -10587,11 +10582,11 @@
       </c>
       <c r="G28" s="14" t="n">
         <f aca="false">IFERROR(G27/G10,0)</f>
-        <v>0.516147110012979</v>
+        <v>0.51614711001298</v>
       </c>
       <c r="H28" s="14" t="n">
         <f aca="false">IFERROR(H27/H10,0)</f>
-        <v>0.433800042983057</v>
+        <v>0.433800042983058</v>
       </c>
       <c r="I28" s="14" t="n">
         <f aca="false">IFERROR(I27/I10,0)</f>
@@ -10599,43 +10594,43 @@
       </c>
       <c r="J28" s="14" t="n">
         <f aca="false">IFERROR(J27/J10,0)</f>
-        <v>0.432524905679584</v>
+        <v>0.432524905679585</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="20" t="str">
+      <c r="D29" s="20" t="n">
         <f aca="false">IF(D19&gt;0,D17/D19,"-")</f>
-        <v>-</v>
+        <v>1.90946065826859</v>
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">IF(E19&gt;0,E17/E19,"-")</f>
-        <v>13.1623426387592</v>
+        <v>13.2163411593476</v>
       </c>
       <c r="F29" s="20" t="n">
         <f aca="false">IF(F19&gt;0,F17/F19,"-")</f>
-        <v>17.3531871551044</v>
+        <v>17.4192737617532</v>
       </c>
       <c r="G29" s="20" t="n">
         <f aca="false">IF(G19&gt;0,G17/G19,"-")</f>
-        <v>26.0792250992083</v>
+        <v>26.1639828880234</v>
       </c>
       <c r="H29" s="20" t="n">
         <f aca="false">IF(H19&gt;0,H17/H19,"-")</f>
-        <v>27.6956242184746</v>
+        <v>27.8137578155258</v>
       </c>
       <c r="I29" s="20" t="n">
         <f aca="false">IF(I19&gt;0,I17/I19,"-")</f>
-        <v>46.6663296991389</v>
+        <v>46.8605360248852</v>
       </c>
       <c r="J29" s="20" t="n">
         <f aca="false">IF(J19&gt;0,J17/J19,"-")</f>
-        <v>137.095857731708</v>
+        <v>137.651930520536</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10676,7 +10671,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>61</v>
@@ -10691,7 +10686,7 @@
       </c>
       <c r="F31" s="20" t="n">
         <f aca="false">IFERROR(F30/F27,0)</f>
-        <v>0.50906058163653</v>
+        <v>0.509060581636531</v>
       </c>
       <c r="G31" s="20" t="n">
         <f aca="false">IFERROR(G30/G27,0)</f>
@@ -10712,7 +10707,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -10753,90 +10748,90 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="C5" s="92" t="n">
+        <v>455</v>
+      </c>
+      <c r="C5" s="91" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="C6" s="92" t="n">
+        <v>456</v>
+      </c>
+      <c r="C6" s="91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="C7" s="92" t="n">
+        <v>457</v>
+      </c>
+      <c r="C7" s="91" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="C8" s="92" t="n">
+        <v>458</v>
+      </c>
+      <c r="C8" s="91" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="C9" s="92" t="n">
+        <v>459</v>
+      </c>
+      <c r="C9" s="91" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" s="92" t="n">
+        <v>460</v>
+      </c>
+      <c r="C10" s="91" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="C11" s="92" t="n">
+        <v>461</v>
+      </c>
+      <c r="C11" s="91" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="C12" s="92" t="n">
+        <v>462</v>
+      </c>
+      <c r="C12" s="91" t="n">
         <v>540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>46</v>
@@ -10873,7 +10868,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>0</v>
@@ -10902,7 +10897,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C17" s="13" t="n">
         <v>0</v>
@@ -10931,7 +10926,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>0</v>
@@ -10960,7 +10955,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C19" s="61" t="n">
         <v>0</v>
@@ -10996,7 +10991,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0</v>
@@ -11025,7 +11020,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0</v>
@@ -11054,7 +11049,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C22" s="61" t="n">
         <v>0</v>
@@ -11090,7 +11085,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C23" s="16" t="n">
         <v>0</v>
@@ -11126,7 +11121,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="25" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C25" s="21"/>
       <c r="D25" s="21" t="n">
@@ -11160,7 +11155,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13" t="n">
@@ -11187,7 +11182,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="61" t="n">
@@ -11221,7 +11216,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -11262,15 +11257,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="60" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11315,7 +11310,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>34</v>
@@ -11351,7 +11346,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -11387,7 +11382,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -11423,7 +11418,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>34</v>
@@ -11458,10 +11453,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="91" t="s">
-        <v>483</v>
-      </c>
-      <c r="C10" s="78" t="s">
+      <c r="B10" s="90" t="s">
+        <v>481</v>
+      </c>
+      <c r="C10" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="61" t="n">
@@ -11495,79 +11490,79 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">-ProfLoss!D11</f>
-        <v>-11316650.7201236</v>
+        <v>-11266042.9168156</v>
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">-ProfLoss!E11</f>
-        <v>-43392941.6724242</v>
+        <v>-43241118.2625002</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">-ProfLoss!F11</f>
-        <v>-49091211.8766119</v>
+        <v>-48939388.4666879</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">-ProfLoss!G11</f>
-        <v>-58338443.9283732</v>
+        <v>-58186620.5184492</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">-ProfLoss!H11</f>
-        <v>-59738918.0634507</v>
+        <v>-59587094.6535267</v>
       </c>
       <c r="I11" s="13" t="n">
         <f aca="false">-ProfLoss!I11</f>
-        <v>-60820556.2151245</v>
+        <v>-60668732.8052005</v>
       </c>
       <c r="J11" s="13" t="n">
         <f aca="false">-ProfLoss!J11</f>
-        <v>-61934685.8487086</v>
+        <v>-61782862.4387846</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="91" t="s">
-        <v>484</v>
-      </c>
-      <c r="C12" s="78" t="s">
+      <c r="B12" s="90" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="61" t="n">
         <f aca="false">D10+D11</f>
-        <v>-11963289.4209364</v>
+        <v>-11912681.6176284</v>
       </c>
       <c r="E12" s="61" t="n">
         <f aca="false">E10+E11</f>
-        <v>55808050.9964777</v>
+        <v>55959874.4064017</v>
       </c>
       <c r="F12" s="61" t="n">
         <f aca="false">F10+F11</f>
-        <v>47429892.3285699</v>
+        <v>47581715.7384939</v>
       </c>
       <c r="G12" s="61" t="n">
         <f aca="false">G10+G11</f>
-        <v>61349080.5112142</v>
+        <v>61500903.9211382</v>
       </c>
       <c r="H12" s="61" t="n">
         <f aca="false">H10+H11</f>
-        <v>60356948.0954341</v>
+        <v>60508771.5053581</v>
       </c>
       <c r="I12" s="61" t="n">
         <f aca="false">I10+I11</f>
-        <v>61482313.9684851</v>
+        <v>61634137.3784091</v>
       </c>
       <c r="J12" s="61" t="n">
         <f aca="false">J10+J11</f>
-        <v>63053205.7600641</v>
+        <v>63205029.1699881</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>34</v>
@@ -11603,7 +11598,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>34</v>
@@ -11639,7 +11634,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>34</v>
@@ -11669,115 +11664,115 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">-ProfLoss!D21</f>
-        <v>-2205838.25258854</v>
+        <v>-1981898.72295066</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">-ProfLoss!E21</f>
-        <v>-14757263.3710805</v>
+        <v>-14780036.8825691</v>
       </c>
       <c r="F16" s="13" t="n">
         <f aca="false">-ProfLoss!F21</f>
-        <v>-16276350.5249837</v>
+        <v>-16299124.0364723</v>
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">-ProfLoss!G21</f>
-        <v>-20554660.7683254</v>
+        <v>-20577434.279814</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">-ProfLoss!H21</f>
-        <v>-18721079.1836114</v>
+        <v>-18743852.6951</v>
       </c>
       <c r="I16" s="13" t="n">
         <f aca="false">-ProfLoss!I21</f>
-        <v>-19219212.3536359</v>
+        <v>-19241985.8651245</v>
       </c>
       <c r="J16" s="13" t="n">
         <f aca="false">-ProfLoss!J21</f>
-        <v>-19742934.7725243</v>
+        <v>-19765708.2840129</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="13" t="n">
-        <f aca="false">Depreciate!$G$19</f>
-        <v>5287922.61812281</v>
+        <f aca="false">Depreciate!$G$18</f>
+        <v>5237314.81481482</v>
       </c>
       <c r="E17" s="13" t="n">
-        <f aca="false">Depreciate!$H$19</f>
-        <v>16022553.5686541</v>
+        <f aca="false">Depreciate!$H$18</f>
+        <v>15870730.1587302</v>
       </c>
       <c r="F17" s="13" t="n">
-        <f aca="false">Depreciate!$I$19</f>
-        <v>16163696.425797</v>
+        <f aca="false">Depreciate!$I$18</f>
+        <v>16011873.015873</v>
       </c>
       <c r="G17" s="13" t="n">
-        <f aca="false">Depreciate!$J$19</f>
-        <v>16304839.2829399</v>
+        <f aca="false">Depreciate!$J$18</f>
+        <v>16153015.8730159</v>
       </c>
       <c r="H17" s="13" t="n">
-        <f aca="false">Depreciate!$K$19</f>
-        <v>16445982.1400827</v>
+        <f aca="false">Depreciate!$K$18</f>
+        <v>16294158.7301587</v>
       </c>
       <c r="I17" s="13" t="n">
-        <f aca="false">Depreciate!$L$19</f>
-        <v>16587124.9972256</v>
+        <f aca="false">Depreciate!$L$18</f>
+        <v>16435301.5873016</v>
       </c>
       <c r="J17" s="13" t="n">
-        <f aca="false">Depreciate!$M$19</f>
-        <v>16728267.8543684</v>
+        <f aca="false">Depreciate!$M$18</f>
+        <v>16576444.4444444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="82" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">SUM(D12:D17)</f>
-        <v>-16752460.6342135</v>
+        <v>-16528521.1045756</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">SUM(E12:E17)</f>
-        <v>52390242.0836931</v>
+        <v>52367468.5722045</v>
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">SUM(F12:F17)</f>
-        <v>42237651.1643225</v>
+        <v>42214877.6528339</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">SUM(G12:G17)</f>
-        <v>40056297.6941421</v>
+        <v>40033524.1826535</v>
       </c>
       <c r="H18" s="16" t="n">
         <f aca="false">SUM(H12:H17)</f>
-        <v>33451740.2727095</v>
+        <v>33428966.7612209</v>
       </c>
       <c r="I18" s="16" t="n">
         <f aca="false">SUM(I12:I17)</f>
-        <v>33632223.371841</v>
+        <v>33609449.8603524</v>
       </c>
       <c r="J18" s="16" t="n">
         <f aca="false">SUM(J12:J17)</f>
-        <v>34187694.5143001</v>
+        <v>34164921.0028116</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>34</v>
@@ -11807,7 +11802,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>34</v>
@@ -11843,50 +11838,50 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="13" t="n">
-        <f aca="false">-Depreciate!$G$23</f>
+        <f aca="false">-Depreciate!$G$22</f>
         <v>-141613333.333333</v>
       </c>
       <c r="E21" s="13" t="n">
-        <f aca="false">-Depreciate!$H$23</f>
+        <f aca="false">-Depreciate!$H$22</f>
         <v>-1411428.57142857</v>
       </c>
       <c r="F21" s="13" t="n">
-        <f aca="false">-Depreciate!$I$23</f>
+        <f aca="false">-Depreciate!$I$22</f>
         <v>-1411428.57142857</v>
       </c>
       <c r="G21" s="13" t="n">
-        <f aca="false">-Depreciate!$J$23</f>
+        <f aca="false">-Depreciate!$J$22</f>
         <v>-1411428.57142857</v>
       </c>
       <c r="H21" s="13" t="n">
-        <f aca="false">-Depreciate!$K$23</f>
+        <f aca="false">-Depreciate!$K$22</f>
         <v>-1411428.57142857</v>
       </c>
       <c r="I21" s="13" t="n">
-        <f aca="false">-Depreciate!$L$23</f>
+        <f aca="false">-Depreciate!$L$22</f>
         <v>-1411428.57142857</v>
       </c>
       <c r="J21" s="13" t="n">
-        <f aca="false">-Depreciate!$M$23</f>
+        <f aca="false">-Depreciate!$M$22</f>
         <v>-1411428.57142857</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">-ProfLoss!D19</f>
-        <v>-0</v>
+        <v>-3036468.19847976</v>
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">-ProfLoss!E19</f>
@@ -11915,14 +11910,13 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="13" t="n">
-        <f aca="false">-LOANS!$C$106</f>
-        <v>-3036468.19847976</v>
+        <v>0</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>0</v>
@@ -11944,44 +11938,44 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="91" t="s">
-        <v>493</v>
-      </c>
-      <c r="C24" s="78" t="s">
+      <c r="B24" s="90" t="s">
+        <v>491</v>
+      </c>
+      <c r="C24" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="61" t="n">
         <f aca="false">D18+D19+D20+D21+D22+D23</f>
-        <v>10043302.5024297</v>
+        <v>10267242.0320676</v>
       </c>
       <c r="E24" s="61" t="n">
         <f aca="false">E18+E19+E20+E21+E22+E23</f>
-        <v>48167191.8554225</v>
+        <v>48144418.3439339</v>
       </c>
       <c r="F24" s="61" t="n">
         <f aca="false">F18+F19+F20+F21+F22+F23</f>
-        <v>38528882.5171568</v>
+        <v>38506109.0056681</v>
       </c>
       <c r="G24" s="61" t="n">
         <f aca="false">G18+G19+G20+G21+G22+G23</f>
-        <v>36853607.0800563</v>
+        <v>36830833.5685677</v>
       </c>
       <c r="H24" s="61" t="n">
         <f aca="false">H18+H19+H20+H21+H22+H23</f>
-        <v>30755127.6917037</v>
+        <v>30732354.1802151</v>
       </c>
       <c r="I24" s="61" t="n">
         <f aca="false">I18+I19+I20+I21+I22+I23</f>
-        <v>31439031.3365268</v>
+        <v>31416257.8250382</v>
       </c>
       <c r="J24" s="61" t="n">
         <f aca="false">J18+J19+J20+J21+J22+J23</f>
-        <v>32503237.9994542</v>
+        <v>32480464.4879657</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>34</v>
@@ -12019,36 +12013,36 @@
       <c r="B26" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="82" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="16" t="n">
         <f aca="false">D24+D25</f>
-        <v>10043302.5024297</v>
+        <v>10267242.0320676</v>
       </c>
       <c r="E26" s="16" t="n">
         <f aca="false">E24+E25</f>
-        <v>41036542.4656462</v>
+        <v>41013768.9541576</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">F24+F25</f>
-        <v>31398233.1273804</v>
+        <v>31375459.6158918</v>
       </c>
       <c r="G26" s="16" t="n">
         <f aca="false">G24+G25</f>
-        <v>29722957.6902799</v>
+        <v>29700184.1787913</v>
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">H24+H25</f>
-        <v>23624478.3019273</v>
+        <v>23601704.7904388</v>
       </c>
       <c r="I26" s="16" t="n">
         <f aca="false">I24+I25</f>
-        <v>24308381.9467505</v>
+        <v>24285608.4352619</v>
       </c>
       <c r="J26" s="16" t="n">
         <f aca="false">J24+J25</f>
-        <v>25372588.6096779</v>
+        <v>25349815.0981893</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12060,36 +12054,36 @@
       </c>
       <c r="D27" s="21" t="n">
         <f aca="false">D26</f>
-        <v>10043302.5024297</v>
+        <v>10267242.0320676</v>
       </c>
       <c r="E27" s="21" t="n">
         <f aca="false">D27+E26</f>
-        <v>51079844.9680759</v>
+        <v>51281010.9862252</v>
       </c>
       <c r="F27" s="21" t="n">
         <f aca="false">E27+F26</f>
-        <v>82478078.0954563</v>
+        <v>82656470.6021169</v>
       </c>
       <c r="G27" s="21" t="n">
         <f aca="false">F27+G26</f>
-        <v>112201035.785736</v>
+        <v>112356654.780908</v>
       </c>
       <c r="H27" s="21" t="n">
         <f aca="false">G27+H26</f>
-        <v>135825514.087664</v>
+        <v>135958359.571347</v>
       </c>
       <c r="I27" s="21" t="n">
         <f aca="false">H27+I26</f>
-        <v>160133896.034414</v>
+        <v>160243968.006609</v>
       </c>
       <c r="J27" s="21" t="n">
         <f aca="false">I27+J26</f>
-        <v>185506484.644092</v>
+        <v>185593783.104798</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>61</v>
@@ -12100,32 +12094,32 @@
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">IFERROR(E18/-(E22+E25),0)</f>
-        <v>5.26944415798368</v>
+        <v>5.26715358358857</v>
       </c>
       <c r="F29" s="20" t="n">
         <f aca="false">IFERROR(F18/-(F22+F25),0)</f>
-        <v>4.48002740338466</v>
+        <v>4.47761188185996</v>
       </c>
       <c r="G29" s="20" t="n">
         <f aca="false">IFERROR(G18/-(G22+G25),0)</f>
-        <v>4.48965426270951</v>
+        <v>4.48710172543529</v>
       </c>
       <c r="H29" s="20" t="n">
         <f aca="false">IFERROR(H18/-(H22+H25),0)</f>
-        <v>3.97485770990652</v>
+        <v>3.97215167826261</v>
       </c>
       <c r="I29" s="20" t="n">
         <f aca="false">IFERROR(I18/-(I22+I25),0)</f>
-        <v>4.25056477636599</v>
+        <v>4.24768657575767</v>
       </c>
       <c r="J29" s="20" t="n">
         <f aca="false">IFERROR(J18/-(J22+J25),0)</f>
-        <v>4.61766403041674</v>
+        <v>4.61458805742877</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>61</v>
@@ -12136,45 +12130,45 @@
       </c>
       <c r="E30" s="20" t="n">
         <f aca="false">IFERROR((E18+E21)/-(E22+E25),0)</f>
-        <v>5.12748176681465</v>
+        <v>5.12519119241954</v>
       </c>
       <c r="F30" s="20" t="n">
         <f aca="false">IFERROR((F18+F21)/-(F22+F25),0)</f>
-        <v>4.3303211933182</v>
+        <v>4.3279056717935</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">IFERROR((G18+G21)/-(G22+G25),0)</f>
-        <v>4.33145625972355</v>
+        <v>4.32890372244933</v>
       </c>
       <c r="H30" s="20" t="n">
         <f aca="false">IFERROR((H18+H21)/-(H22+H25),0)</f>
-        <v>3.8071466224298</v>
+        <v>3.80444059078588</v>
       </c>
       <c r="I30" s="20" t="n">
         <f aca="false">IFERROR((I18+I21)/-(I22+I25),0)</f>
-        <v>4.07218321343031</v>
+        <v>4.069305012822</v>
       </c>
       <c r="J30" s="20" t="n">
         <f aca="false">IFERROR((J18+J21)/-(J22+J25),0)</f>
-        <v>4.42702517516834</v>
+        <v>4.42394920218037</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="25" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D31" s="96" t="n">
         <f aca="false">MIN(E30:J30)</f>
-        <v>3.8071466224298</v>
+        <v>3.80444059078588</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="25" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D32" s="96" t="n">
         <f aca="false">AVERAGE(E30:J30)</f>
-        <v>4.34926903848081</v>
+        <v>4.34661589874177</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12218,10 +12212,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12229,7 +12223,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C4" s="21" t="n">
         <f aca="false">CostTotal!C26</f>
@@ -12256,16 +12250,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">CostTotal!F22</f>
-        <v>28962764.416573</v>
+        <v>28780576.3246643</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">CostTotal!G22</f>
@@ -12274,7 +12268,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">C4-C8</f>
@@ -12283,41 +12277,41 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">IFERROR(C7/C9,0)</f>
-        <v>0.393358554791275</v>
+        <v>0.390884162378221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">C10*C4</f>
-        <v>48027557.7467661</v>
+        <v>47725444.0058583</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="C12" s="80" t="n">
+        <v>503</v>
+      </c>
+      <c r="C12" s="79" t="n">
         <f aca="false">C10*ProdPlan!G13</f>
-        <v>1260.03667086699</v>
-      </c>
-      <c r="D12" s="93" t="s">
-        <v>228</v>
+        <v>1252.1105049286</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">1-C10</f>
-        <v>0.606641445208725</v>
+        <v>0.609115837621779</v>
       </c>
     </row>
   </sheetData>
@@ -12347,12 +12341,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="60" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12397,28 +12391,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C6" s="19"/>
-      <c r="D6" s="92" t="n">
+      <c r="D6" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="92" t="n">
+      <c r="E6" s="91" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="92" t="n">
+      <c r="F6" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="92" t="n">
+      <c r="G6" s="91" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="92" t="n">
+      <c r="H6" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="92" t="n">
+      <c r="I6" s="91" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="92" t="n">
+      <c r="J6" s="91" t="n">
         <v>7</v>
       </c>
     </row>
@@ -12431,36 +12425,36 @@
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-16752460.6342135</v>
+        <v>-16528521.1045756</v>
       </c>
       <c r="E7" s="13" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>52390242.0836931</v>
+        <v>52367468.5722045</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>42237651.1643225</v>
+        <v>42214877.6528339</v>
       </c>
       <c r="G7" s="13" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>40056297.6941421</v>
+        <v>40033524.1826535</v>
       </c>
       <c r="H7" s="13" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>33451740.2727095</v>
+        <v>33428966.7612209</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>33632223.371841</v>
+        <v>33609449.8603524</v>
       </c>
       <c r="J7" s="13" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>34187694.5143001</v>
+        <v>34164921.0028116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>34</v>
@@ -12495,47 +12489,47 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="91" t="s">
-        <v>511</v>
-      </c>
-      <c r="C9" s="78" t="s">
+      <c r="B9" s="90" t="s">
+        <v>509</v>
+      </c>
+      <c r="C9" s="76" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="61" t="n">
         <f aca="false">D7+D8</f>
-        <v>-158365793.967547</v>
+        <v>-158141854.437909</v>
       </c>
       <c r="E9" s="61" t="n">
         <f aca="false">E7+E8</f>
-        <v>50978813.5122645</v>
+        <v>50956040.0007759</v>
       </c>
       <c r="F9" s="61" t="n">
         <f aca="false">F7+F8</f>
-        <v>40826222.5928939</v>
+        <v>40803449.0814053</v>
       </c>
       <c r="G9" s="61" t="n">
         <f aca="false">G7+G8</f>
-        <v>38644869.1227135</v>
+        <v>38622095.6112249</v>
       </c>
       <c r="H9" s="61" t="n">
         <f aca="false">H7+H8</f>
-        <v>32040311.7012809</v>
+        <v>32017538.1897924</v>
       </c>
       <c r="I9" s="61" t="n">
         <f aca="false">I7+I8</f>
-        <v>32220794.8004125</v>
+        <v>32198021.2889238</v>
       </c>
       <c r="J9" s="61" t="n">
         <f aca="false">J7+J8</f>
-        <v>32776265.9428716</v>
+        <v>32753492.431383</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>0.113723926092414</v>
@@ -12567,7 +12561,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="97" t="n">
@@ -12601,115 +12595,115 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">D9*D11</f>
-        <v>-142194838.64658</v>
+        <v>-141993765.899204</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">E9*E11</f>
-        <v>41099318.8289078</v>
+        <v>41080958.7348797</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">F9*F11</f>
-        <v>29553338.6258225</v>
+        <v>29536853.3069765</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">G9*G11</f>
-        <v>25117802.5444179</v>
+        <v>25103000.5648072</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">H9*H11</f>
-        <v>18698595.3785439</v>
+        <v>18685304.8500171</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">I9*I11</f>
-        <v>16883829.2321641</v>
+        <v>16871895.8183122</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">J9*J11</f>
-        <v>15421145.220194</v>
+        <v>15410430.3441172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">D9</f>
-        <v>-158365793.967547</v>
+        <v>-158141854.437909</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">D13+E9</f>
-        <v>-107386980.455282</v>
+        <v>-107185814.437133</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">E13+F9</f>
-        <v>-66560757.8623881</v>
+        <v>-66382365.3557274</v>
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">F13+G9</f>
-        <v>-27915888.7396746</v>
+        <v>-27760269.7445025</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">G13+H9</f>
-        <v>4124422.96160636</v>
+        <v>4257268.44528983</v>
       </c>
       <c r="I13" s="13" t="n">
         <f aca="false">H13+I9</f>
-        <v>36345217.7620188</v>
+        <v>36455289.7342137</v>
       </c>
       <c r="J13" s="13" t="n">
         <f aca="false">I13+J9</f>
-        <v>69121483.7048904</v>
+        <v>69208782.1655967</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="13" t="n">
         <f aca="false">D12</f>
-        <v>-142194838.64658</v>
+        <v>-141993765.899204</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">D14+E12</f>
-        <v>-101095519.817672</v>
+        <v>-100912807.164324</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">E14+F12</f>
-        <v>-71542181.1918497</v>
+        <v>-71375953.8573477</v>
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">F14+G12</f>
-        <v>-46424378.6474318</v>
+        <v>-46272953.2925405</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">G14+H12</f>
-        <v>-27725783.2688879</v>
+        <v>-27587648.4425234</v>
       </c>
       <c r="I14" s="13" t="n">
         <f aca="false">H14+I12</f>
-        <v>-10841954.0367238</v>
+        <v>-10715752.6242113</v>
       </c>
       <c r="J14" s="13" t="n">
         <f aca="false">I14+J12</f>
-        <v>4579191.18347016</v>
+        <v>4694677.7199059</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="98" t="str">
@@ -12730,7 +12724,7 @@
       </c>
       <c r="H15" s="98" t="n">
         <f aca="false">IF(AND(G13&lt;0,H13&gt;=0),G6-G13/H9,"")</f>
-        <v>4.87127394389732</v>
+        <v>4.86703323597043</v>
       </c>
       <c r="I15" s="98" t="str">
         <f aca="false">IF(AND(H13&lt;0,I13&gt;=0),H6-H13/I9,"")</f>
@@ -12743,7 +12737,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="98" t="str">
@@ -12772,27 +12766,27 @@
       </c>
       <c r="J16" s="98" t="n">
         <f aca="false">IF(AND(I14&lt;0,J14&gt;=0),I6-I14/J12,"")</f>
-        <v>6.7030576446765</v>
+        <v>6.69535713052309</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="15" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16" t="n">
         <f aca="false">SUM(D12:J12)</f>
-        <v>4579191.18347016</v>
+        <v>4694677.7199059</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="17" t="n">
         <f aca="false">IFERROR(IRR(D9:J9),"-")</f>
-        <v>0.125981395703447</v>
+        <v>0.12630736634052</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12802,17 +12796,17 @@
       <c r="C20" s="15"/>
       <c r="D20" s="99" t="n">
         <f aca="false">IFERROR(SUM(E12:J12)/-D12,0)</f>
-        <v>1.03220363852201</v>
+        <v>1.03306256222008</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="100" t="n">
         <f aca="false">IF(COUNT(E15:J15)&gt;0,SUM(E15:J15),"&gt; 7")</f>
-        <v>4.87127394389732</v>
+        <v>4.86703323597043</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12822,7 +12816,7 @@
       <c r="C22" s="15"/>
       <c r="D22" s="100" t="n">
         <f aca="false">IF(COUNT(E16:J16)&gt;0,SUM(E16:J16),"&gt; 7")</f>
-        <v>6.7030576446765</v>
+        <v>6.69535713052309</v>
       </c>
     </row>
   </sheetData>
@@ -14897,266 +14891,220 @@
         <v>893904.761904762</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="D18" s="55" t="n">
+        <f aca="false">SUM(D7:D17)</f>
+        <v>150081904.761905</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="55" t="n">
+        <f aca="false">SUM(G7:G17)</f>
+        <v>5237314.81481482</v>
+      </c>
+      <c r="H18" s="55" t="n">
+        <f aca="false">SUM(H7:H17)</f>
+        <v>15870730.1587302</v>
+      </c>
+      <c r="I18" s="55" t="n">
+        <f aca="false">SUM(I7:I17)</f>
+        <v>16011873.015873</v>
+      </c>
+      <c r="J18" s="55" t="n">
+        <f aca="false">SUM(J7:J17)</f>
+        <v>16153015.8730159</v>
+      </c>
+      <c r="K18" s="55" t="n">
+        <f aca="false">SUM(K7:K17)</f>
+        <v>16294158.7301587</v>
+      </c>
+      <c r="L18" s="55" t="n">
+        <f aca="false">SUM(L7:L17)</f>
+        <v>16435301.5873016</v>
+      </c>
+      <c r="M18" s="55" t="n">
+        <f aca="false">SUM(M7:M17)</f>
+        <v>16576444.4444444</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D18" s="53" t="n">
-        <f aca="false">LOANS!$C$106</f>
-        <v>3036468.19847976</v>
-      </c>
-      <c r="E18" s="76" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" s="52" t="n">
-        <f aca="false">1/E18</f>
-        <v>0.05</v>
-      </c>
-      <c r="G18" s="53" t="n">
-        <f aca="false">D18/E18*4/12</f>
-        <v>50607.803307996</v>
-      </c>
-      <c r="H18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-      <c r="I18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-      <c r="J18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-      <c r="K18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-      <c r="L18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-      <c r="M18" s="53" t="n">
-        <f aca="false">D18/E18</f>
-        <v>151823.409923988</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="78" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="55" t="n">
-        <f aca="false">SUM(D7:D18)</f>
-        <v>153118372.960385</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="55" t="n">
-        <f aca="false">SUM(G7:G18)</f>
-        <v>5287922.61812281</v>
-      </c>
-      <c r="H19" s="55" t="n">
-        <f aca="false">SUM(H7:H18)</f>
-        <v>16022553.5686541</v>
-      </c>
-      <c r="I19" s="55" t="n">
-        <f aca="false">SUM(I7:I18)</f>
-        <v>16163696.425797</v>
-      </c>
-      <c r="J19" s="55" t="n">
-        <f aca="false">SUM(J7:J18)</f>
-        <v>16304839.2829399</v>
-      </c>
-      <c r="K19" s="55" t="n">
-        <f aca="false">SUM(K7:K18)</f>
-        <v>16445982.1400827</v>
-      </c>
-      <c r="L19" s="55" t="n">
-        <f aca="false">SUM(L7:L18)</f>
-        <v>16587124.9972256</v>
-      </c>
-      <c r="M19" s="55" t="n">
-        <f aca="false">SUM(M7:M18)</f>
-        <v>16728267.8543684</v>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="53" t="n">
+        <f aca="false">G18-G20</f>
+        <v>5237314.81481482</v>
+      </c>
+      <c r="H19" s="53" t="n">
+        <f aca="false">H18-H20</f>
+        <v>15870730.1587302</v>
+      </c>
+      <c r="I19" s="53" t="n">
+        <f aca="false">I18-I20</f>
+        <v>16011873.015873</v>
+      </c>
+      <c r="J19" s="53" t="n">
+        <f aca="false">J18-J20</f>
+        <v>16153015.8730159</v>
+      </c>
+      <c r="K19" s="53" t="n">
+        <f aca="false">K18-K20</f>
+        <v>16294158.7301587</v>
+      </c>
+      <c r="L19" s="53" t="n">
+        <f aca="false">L18-L20</f>
+        <v>16435301.5873016</v>
+      </c>
+      <c r="M19" s="53" t="n">
+        <f aca="false">M18-M20</f>
+        <v>16576444.4444444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="78"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="53" t="n">
-        <f aca="false">G19-G21</f>
-        <v>5287922.61812281</v>
-      </c>
-      <c r="H20" s="53" t="n">
-        <f aca="false">H19-H21</f>
-        <v>16022553.5686541</v>
-      </c>
-      <c r="I20" s="53" t="n">
-        <f aca="false">I19-I21</f>
-        <v>16163696.425797</v>
-      </c>
-      <c r="J20" s="53" t="n">
-        <f aca="false">J19-J21</f>
-        <v>16304839.2829399</v>
-      </c>
-      <c r="K20" s="53" t="n">
-        <f aca="false">K19-K21</f>
-        <v>16445982.1400827</v>
-      </c>
-      <c r="L20" s="53" t="n">
-        <f aca="false">L19-L21</f>
-        <v>16587124.9972256</v>
-      </c>
-      <c r="M20" s="53" t="n">
-        <f aca="false">M19-M21</f>
-        <v>16728267.8543684</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="53" t="n">
+        <v>141613333.333333</v>
+      </c>
+      <c r="H22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+      <c r="I22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+      <c r="J22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+      <c r="K22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+      <c r="L22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+      <c r="M22" s="53" t="n">
+        <v>1411428.57142857</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="53" t="n">
+        <f aca="false">SUM($G$18:G18)</f>
+        <v>5237314.81481482</v>
+      </c>
+      <c r="H23" s="53" t="n">
+        <f aca="false">SUM($G$18:H18)</f>
+        <v>21108044.973545</v>
+      </c>
+      <c r="I23" s="53" t="n">
+        <f aca="false">SUM($G$18:I18)</f>
+        <v>37119917.989418</v>
+      </c>
+      <c r="J23" s="53" t="n">
+        <f aca="false">SUM($G$18:J18)</f>
+        <v>53272933.8624339</v>
+      </c>
+      <c r="K23" s="53" t="n">
+        <f aca="false">SUM($G$18:K18)</f>
+        <v>69567092.5925926</v>
+      </c>
+      <c r="L23" s="53" t="n">
+        <f aca="false">SUM($G$18:L18)</f>
+        <v>86002394.1798942</v>
+      </c>
+      <c r="M23" s="53" t="n">
+        <f aca="false">SUM($G$18:M18)</f>
+        <v>102578838.624339</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="53" t="n">
-        <v>141613333.333333</v>
-      </c>
-      <c r="H23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-      <c r="I23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-      <c r="J23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-      <c r="K23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-      <c r="L23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-      <c r="M23" s="53" t="n">
-        <v>1411428.57142857</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
       <c r="E24" s="19"/>
-      <c r="F24" s="75"/>
+      <c r="F24" s="78"/>
       <c r="G24" s="53" t="n">
-        <f aca="false">SUM($G$19:G19)</f>
-        <v>5287922.61812281</v>
+        <f aca="false">G22-G18</f>
+        <v>136376018.518518</v>
       </c>
       <c r="H24" s="53" t="n">
-        <f aca="false">SUM($G$19:H19)</f>
-        <v>21310476.186777</v>
+        <f aca="false">G24+H22-H18</f>
+        <v>121916716.931217</v>
       </c>
       <c r="I24" s="53" t="n">
-        <f aca="false">SUM($G$19:I19)</f>
-        <v>37474172.612574</v>
+        <f aca="false">H24+I22-I18</f>
+        <v>107316272.486772</v>
       </c>
       <c r="J24" s="53" t="n">
-        <f aca="false">SUM($G$19:J19)</f>
-        <v>53779011.8955138</v>
+        <f aca="false">I24+J22-J18</f>
+        <v>92574685.1851849</v>
       </c>
       <c r="K24" s="53" t="n">
-        <f aca="false">SUM($G$19:K19)</f>
-        <v>70224994.0355965</v>
+        <f aca="false">J24+K22-K18</f>
+        <v>77691955.0264547</v>
       </c>
       <c r="L24" s="53" t="n">
-        <f aca="false">SUM($G$19:L19)</f>
-        <v>86812119.0328221</v>
+        <f aca="false">K24+L22-L18</f>
+        <v>62668082.0105817</v>
       </c>
       <c r="M24" s="53" t="n">
-        <f aca="false">SUM($G$19:M19)</f>
-        <v>103540386.887191</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="53" t="n">
-        <f aca="false">G23+$D$18-G19</f>
-        <v>139361878.91369</v>
-      </c>
-      <c r="H25" s="53" t="n">
-        <f aca="false">G25+H23-H19</f>
-        <v>124750753.916464</v>
-      </c>
-      <c r="I25" s="53" t="n">
-        <f aca="false">H25+I23-I19</f>
-        <v>109998486.062096</v>
-      </c>
-      <c r="J25" s="53" t="n">
-        <f aca="false">I25+J23-J19</f>
-        <v>95105075.3505846</v>
-      </c>
-      <c r="K25" s="53" t="n">
-        <f aca="false">J25+K23-K19</f>
-        <v>80070521.7819305</v>
-      </c>
-      <c r="L25" s="53" t="n">
-        <f aca="false">K25+L23-L19</f>
-        <v>64894825.3561335</v>
-      </c>
-      <c r="M25" s="53" t="n">
-        <f aca="false">L25+M23-M19</f>
-        <v>49577986.0731936</v>
-      </c>
-    </row>
+        <f aca="false">L24+M22-M18</f>
+        <v>47503066.1375658</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B5:B6"/>
@@ -15201,33 +15149,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15235,15 +15183,15 @@
         <v>11</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" s="80" t="n">
+        <v>226</v>
+      </c>
+      <c r="D5" s="79" t="n">
         <v>4200</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" s="81" t="n">
+        <v>227</v>
+      </c>
+      <c r="F5" s="80" t="n">
         <f aca="false">G20</f>
         <v>38116</v>
       </c>
@@ -15314,23 +15262,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
+        <v>228</v>
+      </c>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>0.157862951062778</v>
@@ -15356,212 +15304,212 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
+        <v>230</v>
+      </c>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="80" t="n">
+        <v>226</v>
+      </c>
+      <c r="D13" s="79" t="n">
         <f aca="false">$D$5*D11</f>
         <v>663.024394463668</v>
       </c>
-      <c r="E13" s="80" t="n">
+      <c r="E13" s="79" t="n">
         <f aca="false">$D$5*E11</f>
         <v>2331.50380622838</v>
       </c>
-      <c r="F13" s="80" t="n">
+      <c r="F13" s="79" t="n">
         <f aca="false">$D$5*F11</f>
         <v>2521.43641868512</v>
       </c>
-      <c r="G13" s="80" t="n">
+      <c r="G13" s="79" t="n">
         <f aca="false">$D$5*G11</f>
         <v>3203.27765983276</v>
       </c>
-      <c r="H13" s="80" t="n">
+      <c r="H13" s="79" t="n">
         <f aca="false">$D$5*H11</f>
         <v>3079.60677269319</v>
       </c>
-      <c r="I13" s="80" t="n">
+      <c r="I13" s="79" t="n">
         <f aca="false">$D$5*I11</f>
         <v>3077.5562283737</v>
       </c>
-      <c r="J13" s="80" t="n">
+      <c r="J13" s="79" t="n">
         <f aca="false">$D$5*J11</f>
         <v>3077.5562283737</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
+        <v>231</v>
+      </c>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="80" t="n">
+        <v>226</v>
+      </c>
+      <c r="D15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="80" t="n">
+        <v>226</v>
+      </c>
+      <c r="D16" s="79" t="n">
         <v>663.024394463668</v>
       </c>
-      <c r="E16" s="80" t="n">
+      <c r="E16" s="79" t="n">
         <v>2331.50380622837</v>
       </c>
-      <c r="F16" s="80" t="n">
+      <c r="F16" s="79" t="n">
         <v>2521.43641868512</v>
       </c>
-      <c r="G16" s="80" t="n">
+      <c r="G16" s="79" t="n">
         <v>3203.27765983275</v>
       </c>
-      <c r="H16" s="80" t="n">
+      <c r="H16" s="79" t="n">
         <v>3079.6067726932</v>
       </c>
-      <c r="I16" s="80" t="n">
+      <c r="I16" s="79" t="n">
         <v>3077.5562283737</v>
       </c>
-      <c r="J16" s="80" t="n">
+      <c r="J16" s="79" t="n">
         <v>3077.5562283737</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
+        <v>234</v>
+      </c>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" s="80" t="n">
+        <v>226</v>
+      </c>
+      <c r="D18" s="79" t="n">
         <f aca="false">0+D13-D15-D16</f>
         <v>0</v>
       </c>
-      <c r="E18" s="80" t="n">
+      <c r="E18" s="79" t="n">
         <f aca="false">D18+E13-E15-E16</f>
         <v>0</v>
       </c>
-      <c r="F18" s="80" t="n">
+      <c r="F18" s="79" t="n">
         <f aca="false">E18+F13-F15-F16</f>
         <v>0</v>
       </c>
-      <c r="G18" s="80" t="n">
+      <c r="G18" s="79" t="n">
         <f aca="false">F18+G13-G15-G16</f>
         <v>0</v>
       </c>
-      <c r="H18" s="80" t="n">
+      <c r="H18" s="79" t="n">
         <f aca="false">G18+H13-H15-H16</f>
         <v>0</v>
       </c>
-      <c r="I18" s="80" t="n">
+      <c r="I18" s="79" t="n">
         <f aca="false">H18+I13-I15-I16</f>
         <v>0</v>
       </c>
-      <c r="J18" s="80" t="n">
+      <c r="J18" s="79" t="n">
         <f aca="false">I18+J13-J15-J16</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
+        <v>235</v>
+      </c>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D20" s="81" t="n">
+        <v>236</v>
+      </c>
+      <c r="D20" s="80" t="n">
         <v>35989</v>
       </c>
-      <c r="E20" s="81" t="n">
+      <c r="E20" s="80" t="n">
         <v>36493</v>
       </c>
-      <c r="F20" s="81" t="n">
+      <c r="F20" s="80" t="n">
         <v>37295</v>
       </c>
-      <c r="G20" s="81" t="n">
+      <c r="G20" s="80" t="n">
         <v>38116</v>
       </c>
-      <c r="H20" s="81" t="n">
+      <c r="H20" s="80" t="n">
         <v>38954</v>
       </c>
-      <c r="I20" s="81" t="n">
+      <c r="I20" s="80" t="n">
         <v>39811</v>
       </c>
-      <c r="J20" s="81" t="n">
+      <c r="J20" s="80" t="n">
         <v>40687</v>
       </c>
     </row>
@@ -15603,10 +15551,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15651,20 +15599,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
+        <v>239</v>
+      </c>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>34</v>
@@ -15736,20 +15684,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
+        <v>241</v>
+      </c>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>34</v>
@@ -15821,9 +15769,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="C14" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="82" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="16" t="n">
@@ -15857,10 +15805,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">IFERROR(D8/D14,0)</f>
@@ -15932,43 +15880,43 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="60" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="G5" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="H5" s="18" t="s">
         <v>252</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -15979,16 +15927,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D7" s="81" t="n">
+        <v>226</v>
+      </c>
+      <c r="D7" s="80" t="n">
         <f aca="false">IFERROR(F7/E7,0)</f>
         <v>28.389042396056</v>
       </c>
-      <c r="E7" s="80" t="n">
+      <c r="E7" s="79" t="n">
         <v>600000</v>
       </c>
       <c r="F7" s="13" t="n">
@@ -15998,22 +15946,22 @@
         <f aca="false">IFERROR(F7/$F$16,0)</f>
         <v>0.540061324245068</v>
       </c>
-      <c r="H7" s="84" t="s">
-        <v>257</v>
+      <c r="H7" s="83" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="81" t="n">
+        <v>226</v>
+      </c>
+      <c r="D8" s="80" t="n">
         <f aca="false">IFERROR(F8/E8,0)</f>
         <v>23.1897641361257</v>
       </c>
-      <c r="E8" s="80" t="n">
+      <c r="E8" s="79" t="n">
         <v>600000</v>
       </c>
       <c r="F8" s="13" t="n">
@@ -16023,22 +15971,22 @@
         <f aca="false">IFERROR(F8/$F$16,0)</f>
         <v>0.441152419076549</v>
       </c>
-      <c r="H8" s="84" t="s">
-        <v>257</v>
+      <c r="H8" s="83" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="81" t="n">
+        <v>226</v>
+      </c>
+      <c r="D9" s="80" t="n">
         <f aca="false">IFERROR(F9/E9,0)</f>
         <v>166.870976942717</v>
       </c>
-      <c r="E9" s="80" t="n">
+      <c r="E9" s="79" t="n">
         <v>3203.27765983275</v>
       </c>
       <c r="F9" s="13" t="n">
@@ -16048,13 +15996,13 @@
         <f aca="false">IFERROR(F9/$F$16,0)</f>
         <v>0.0169479227835633</v>
       </c>
-      <c r="H9" s="84" t="s">
-        <v>257</v>
+      <c r="H9" s="83" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="25" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -16071,7 +16019,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
@@ -16082,16 +16030,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="D13" s="81" t="n">
+        <v>261</v>
+      </c>
+      <c r="D13" s="80" t="n">
         <f aca="false">IFERROR(F13/E13,0)</f>
         <v>0.096634468226577</v>
       </c>
-      <c r="E13" s="80" t="n">
+      <c r="E13" s="79" t="n">
         <v>600000</v>
       </c>
       <c r="F13" s="13" t="n">
@@ -16101,13 +16049,13 @@
         <f aca="false">IFERROR(F13/$F$16,0)</f>
         <v>0.0018383338948204</v>
       </c>
-      <c r="H13" s="84" t="s">
-        <v>257</v>
+      <c r="H13" s="83" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="25" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -16124,11 +16072,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
+        <v>263</v>
+      </c>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
       <c r="F16" s="16" t="n">
         <f aca="false">F10+F14</f>
         <v>31539798.67276</v>
@@ -16137,11 +16085,11 @@
         <f aca="false">IFERROR(F16/$F$16,0)</f>
         <v>1</v>
       </c>
-      <c r="H16" s="85"/>
+      <c r="H16" s="84"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -16152,30 +16100,30 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="13" t="n">
-        <f aca="false">+Depreciate!D19*1%</f>
-        <v>1531183.72960385</v>
+        <f aca="false">+Depreciate!D18*1%</f>
+        <v>1500819.04761905</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -16186,7 +16134,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -16198,14 +16146,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="21" t="n">
         <f aca="false">SUM(F20:F22)</f>
-        <v>5295335.48529033</v>
+        <v>5264970.80330553</v>
       </c>
     </row>
   </sheetData>
